--- a/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
+++ b/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-13" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,12 +78,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.39</v>
+        <v>0.155</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>-0.1389</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>26875000</v>
+        <v>43073400</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H2" t="n">
-        <v>70.36</v>
+        <v>48.11</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.358</v>
+        <v>0.166</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.236</v>
+        <v>0.133</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -599,19 +599,19 @@
       <c r="D3" s="2" t="n">
         <v>0.075</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="3" t="n">
         <v>-0.1176</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>23993300</v>
+        <v>39867100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H3" t="n">
         <v>22.65</v>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0.0163</v>
+        <v>0.18</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-0.1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>22903300</v>
+        <v>20022300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H4" t="n">
-        <v>71.59999999999999</v>
+        <v>43.31</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.582</v>
+        <v>0.195</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.508</v>
+        <v>0.184</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.0833</v>
+        <v>0.495</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.0481</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4788700</v>
+        <v>15562300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H5" t="n">
-        <v>52.28</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.86</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.167</v>
+        <v>0.491</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.133</v>
+        <v>0.48</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.0435</v>
+        <v>0.83</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1688400</v>
+        <v>12712100</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="H6" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>60.43</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.284</v>
+        <v>0.787</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.247</v>
+        <v>0.714</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -779,16 +779,16 @@
       <c r="D7" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1606200</v>
+        <v>10072400</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+        <v>0.29</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -806,39 +806,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0408</v>
+        <v>0.32</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.0725</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1577400</v>
+        <v>8891500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.98</v>
+        <v>0.15</v>
       </c>
       <c r="H8" t="n">
-        <v>61</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+        <v>66.06</v>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.238</v>
+        <v>0.283</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.243</v>
+        <v>0.246</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -851,39 +851,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.0538</v>
+        <v>0.105</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1418100</v>
+        <v>8708600</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.42</v>
+        <v>1.32</v>
       </c>
       <c r="H9" t="n">
-        <v>69.68000000000001</v>
+        <v>37.13</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.366</v>
+        <v>0.114</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.351</v>
+        <v>0.122</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,39 +896,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.2181</v>
+        <v>0.405</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.129</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>748900</v>
+        <v>8186100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.19</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.08</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.858</v>
+        <v>0.363</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2.013</v>
+        <v>0.35</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -941,45 +941,4140 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>2.17</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.0284</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>555000</v>
+        <v>8178500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H11" t="n">
-        <v>78.59</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+        <v>77.58</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.676</v>
+        <v>1.854</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2.31</v>
+        <v>1.659</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0207</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MESTRON</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>7846800</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H12" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>7439600</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5260</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>OWG</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>6462100</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="H14" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>6251000</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.07139999999999999</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>6178200</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H16" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.2128</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>5422800</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>2.013</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0337</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>4966200</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H18" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>4420000</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.0741</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>4265700</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H20" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0526</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>4221800</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.07429999999999999</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>3588700</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H22" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>3535900</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.0253</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>3509700</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H24" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>3394600</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H25" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.156</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>3244700</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.0508</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2637800</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2623600</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H28" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2439200</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0764</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>2406400</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H30" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.05429999999999999</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>2362300</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H31" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>2256100</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>2220300</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.08960000000000001</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>2104000</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.1409</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>2087500</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H35" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1.611</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DATASONIC</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1941200</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1888900</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H37" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0337</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1838100</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H38" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>-0.0246</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1805900</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H39" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>2.794</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2.702</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.0622</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1778100</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H40" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1716100</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H41" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.0659</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1654700</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H42" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1589600</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H43" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>3.606</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0375</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1526700</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H44" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1472500</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H45" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>4.931</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>4.668</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.0649</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1452200</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H46" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>9679</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>WCT</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1432300</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H47" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0463</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1429600</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>2.216</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1414500</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>7.615</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>7.725</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1400300</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H50" t="n">
+        <v>81.42</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1335200</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H51" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>5.807</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0328</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3REN</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.04940000000000001</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1332200</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H52" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>1319600</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H54" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ESCERAM</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1272900</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H55" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1252600</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H56" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.0296</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1201100</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H57" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>2.628</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2.586</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.06610000000000001</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1175000</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H58" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>1134000</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H59" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.0599</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1104200</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H60" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>1090400</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H61" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1.378</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>-0.05429999999999999</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>1080200</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H62" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0636</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>991600</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H63" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>931300</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H64" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>3.031</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.0576</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>912500</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H65" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>5.485</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>5.367</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.0323</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>895000</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H66" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.0902</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>893500</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H67" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.04480000000000001</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>868600</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H68" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>858100</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H69" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>3.873</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>3.592</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>845700</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H70" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>4.884</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>840400</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H71" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>831300</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H72" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>820600</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H73" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.0314</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>786100</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H74" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>778600</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H75" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>3.451</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>3.645</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>776500</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H76" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>2.611</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>769500</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>4.366</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>4.458</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>766000</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H78" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>765900</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>727400</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H80" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>10.305</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>9.561</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>718100</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H81" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>10.203</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>716200</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H82" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>716000</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H83" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>5.624</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>5.334</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.0354</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>709000</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H84" t="n">
+        <v>58.06</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>3.977</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>682600</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H85" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>-0.0541</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>671600</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H86" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0554</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>661900</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H87" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>2.944</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>643800</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H88" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>641600</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H89" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>632800</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H90" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.0373</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>629100</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H91" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>619200</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H92" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.0278</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>615900</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H93" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.0576</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>613500</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H94" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>602500</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H95" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.0472</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>598400</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H96" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.07730000000000001</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>590200</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H97" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>588700</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H98" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>562000</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H99" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>544700</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H100" t="n">
+        <v>59</v>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.1096</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>524500</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0375</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>509300</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H102" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>3.008</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>2.814</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M11"/>
+  <autoFilter ref="A1:M102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
+++ b/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-13" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,8 +83,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.1389</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>43073400</v>
+        <v>59608500</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="H2" t="n">
         <v>48.11</v>
@@ -603,10 +603,10 @@
         <v>-0.1176</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>39867100</v>
+        <v>50800800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H3" t="n">
         <v>22.65</v>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.18</v>
+        <v>0.48</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>20022300</v>
+        <v>28342300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>43.31</v>
+        <v>48.22</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.195</v>
+        <v>0.49</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.184</v>
+        <v>0.48</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.495</v>
+        <v>0.185</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.0481</v>
+        <v>-0.075</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>15562300</v>
+        <v>20042300</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.48</v>
+        <v>0.87</v>
       </c>
       <c r="H5" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.53</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.491</v>
+        <v>0.195</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.48</v>
+        <v>0.184</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.0178</v>
+        <v>-0.0435</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12712100</v>
+        <v>19256800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="H6" t="n">
-        <v>60.43</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.787</v>
+        <v>0.284</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.714</v>
+        <v>0.247</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,33 +768,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
+        <v>0.83</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10072400</v>
+        <v>17623700</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>60.43</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
+      <c r="J7" s="2" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.714</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
@@ -806,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.0725</v>
+        <v>0.395</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8891500</v>
+        <v>14638000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="n">
-        <v>66.06</v>
+        <v>71.42</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
@@ -835,10 +842,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.283</v>
+        <v>0.361</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.246</v>
+        <v>0.243</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -851,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-0.0455</v>
+        <v>2.11</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8708600</v>
+        <v>12862400</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.32</v>
+        <v>0.48</v>
       </c>
       <c r="H9" t="n">
-        <v>37.13</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.53</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.114</v>
+        <v>1.848</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.122</v>
+        <v>1.658</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -905,19 +912,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.405</v>
+        <v>0.415</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.129</v>
+        <v>-0.1075</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8186100</v>
+        <v>12547100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>2.4</v>
+        <v>3.68</v>
       </c>
       <c r="H10" t="n">
-        <v>60.08</v>
+        <v>62.54</v>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
@@ -925,7 +932,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0.35</v>
@@ -941,40 +948,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2.17</v>
+        <v>0.25</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.0284</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8178500</v>
+        <v>10628100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H11" t="n">
-        <v>77.58</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>1.854</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>1.659</v>
-      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,28 +986,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.2</v>
+        <v>0.575</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.0873</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7846800</v>
+        <v>9778200</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2.62</v>
+        <v>0.54</v>
       </c>
       <c r="H12" t="n">
-        <v>55.2</v>
+        <v>51.64</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.092</v>
+        <v>0.522</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,39 +1031,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0</v>
+        <v>0.105</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7439600</v>
+        <v>8715900</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.2</v>
+        <v>1.32</v>
       </c>
       <c r="H13" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.13</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.361</v>
+        <v>0.114</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.243</v>
+        <v>0.122</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,28 +1076,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E14" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>0.0526</v>
-      </c>
       <c r="F14" s="4" t="n">
-        <v>6462100</v>
+        <v>8348200</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>8.41</v>
+        <v>2.79</v>
       </c>
       <c r="H14" t="n">
-        <v>61.56</v>
+        <v>55.2</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.187</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.188</v>
+        <v>0.092</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,28 +1121,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-0.016</v>
+        <v>0.195</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6251000</v>
+        <v>8106800</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.24</v>
+        <v>10.55</v>
       </c>
       <c r="H15" t="n">
-        <v>66.51000000000001</v>
+        <v>58.36</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.585</v>
+        <v>0.186</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.51</v>
+        <v>0.188</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.585</v>
+        <v>1.48</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.2128</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6178200</v>
+        <v>7752600</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.34</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.51</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.581</v>
+        <v>1.859</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.523</v>
+        <v>2.013</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,28 +1211,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.48</v>
+        <v>0.14</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.2128</v>
+        <v>-0.0345</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5422800</v>
+        <v>7683400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="n">
-        <v>20.51</v>
+        <v>42.91</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.859</v>
+        <v>0.154</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2.013</v>
+        <v>0.148</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,28 +1256,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.62</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4966200</v>
+        <v>6871600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>3.07</v>
+        <v>0.26</v>
       </c>
       <c r="H18" t="n">
-        <v>58.46</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.238</v>
+        <v>0.586</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.243</v>
+        <v>0.51</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         <v>-0.0139</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4420000</v>
+        <v>6462900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.59</v>
+        <v>0.86</v>
       </c>
       <c r="H19" t="n">
         <v>57.67</v>
@@ -1346,28 +1346,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.0741</v>
+        <v>-0.0526</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4265700</v>
+        <v>6219800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.55</v>
+        <v>0.16</v>
       </c>
       <c r="H20" t="n">
-        <v>43.62</v>
+        <v>24.17</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.53</v>
+        <v>0.737</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.45</v>
+        <v>0.675</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4221800</v>
+        <v>5918200</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.11</v>
+        <v>0.7</v>
       </c>
       <c r="H21" t="n">
-        <v>24.17</v>
+        <v>47.62</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.737</v>
+        <v>0.68</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,28 +1436,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>2.71</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-0.07429999999999999</v>
+        <v>-0.0217</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3588700</v>
+        <v>5856400</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="H22" t="n">
-        <v>49.29</v>
+        <v>58.44</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>2.634</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.681</v>
+        <v>2.508</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1481,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0</v>
+        <v>0.495</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0833</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3535900</v>
+        <v>5162700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="H23" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.4</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.639</v>
+        <v>0.52</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2.509</v>
+        <v>0.53</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-0.0253</v>
+        <v>0.25</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3509700</v>
+        <v>4980200</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.32</v>
+        <v>3.08</v>
       </c>
       <c r="H24" t="n">
-        <v>30.18</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.46</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.401</v>
+        <v>0.238</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.409</v>
+        <v>0.243</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.32</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3394600</v>
+        <v>4596600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.18</v>
+        <v>0.77</v>
       </c>
       <c r="H25" t="n">
-        <v>46.92</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.868</v>
+        <v>0.293</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.869</v>
+        <v>0.276</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.46</v>
+        <v>0.865</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.156</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3244700</v>
+        <v>4479700</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.58</v>
+        <v>0.24</v>
       </c>
       <c r="H26" t="n">
-        <v>21.23</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.92</v>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.579</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.637</v>
+        <v>0.869</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,39 +1661,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.28</v>
+        <v>0.305</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.0508</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2637800</v>
+        <v>4325100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.3</v>
+        <v>0.73</v>
       </c>
       <c r="H27" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.78</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.278</v>
+        <v>0.324</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.302</v>
+        <v>0.338</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,39 +1706,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-0.0374</v>
+        <v>0.82</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2623600</v>
+        <v>4102100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H28" t="n">
-        <v>44.35</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.068</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.038</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1751,39 +1751,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.0345</v>
+        <v>-0.1111</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2439200</v>
+        <v>3970900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1</v>
+        <v>1.21</v>
       </c>
       <c r="H29" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.91</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.411</v>
+        <v>0.184</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.35</v>
+        <v>0.194</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,39 +1796,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.665</v>
+        <v>0.42</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.0764</v>
+        <v>-0.0345</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2406400</v>
+        <v>3881500</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H30" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.03</v>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.671</v>
+        <v>0.411</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1841,39 +1841,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.435</v>
+        <v>0.39</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0127</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2362300</v>
+        <v>3824400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="H31" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.82</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.45</v>
+        <v>0.401</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.428</v>
+        <v>0.409</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1886,39 +1886,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.82</v>
+        <v>0.53</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2256100</v>
+        <v>3820500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="H32" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.81</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.513</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1931,28 +1931,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.019</v>
+        <v>0.47</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-0.1376</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2220300</v>
+        <v>3759600</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="H33" t="n">
-        <v>57.67</v>
+        <v>22.12</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.514</v>
+        <v>0.58</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.44</v>
+        <v>0.637</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1976,39 +1976,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-0.08960000000000001</v>
+        <v>0.775</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2104000</v>
+        <v>3522000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H34" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.45</v>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.324</v>
+        <v>0.774</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.338</v>
+        <v>0.775</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2021,28 +2021,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1.28</v>
+        <v>0.215</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.1409</v>
+        <v>-0.0444</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2087500</v>
+        <v>3520600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1.18</v>
+        <v>0.14</v>
       </c>
       <c r="H35" t="n">
-        <v>20.62</v>
+        <v>30.21</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.487</v>
+        <v>0.246</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1.611</v>
+        <v>0.301</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2075,19 +2075,19 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.285</v>
+        <v>0.275</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.0833</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1941200</v>
+        <v>3390700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="H36" t="n">
-        <v>48.66</v>
+        <v>45.58</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.291</v>
+        <v>0.29</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0.281</v>
@@ -2111,39 +2111,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.89</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.07769999999999999</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1888900</v>
+        <v>3333700</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="H37" t="n">
-        <v>77.36</v>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.62</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.293</v>
+        <v>0.954</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.276</v>
+        <v>0.825</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2156,28 +2156,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.0337</v>
+        <v>7.41</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0.0207</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1838100</v>
+        <v>3317500</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="H38" t="n">
-        <v>44.89</v>
+        <v>39.76</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.751</v>
+        <v>7.618</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1.777</v>
+        <v>7.725</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2201,28 +2201,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2.78</v>
+        <v>0.145</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-0.0246</v>
+        <v>-0.0333</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1805900</v>
+        <v>3187900</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H39" t="n">
-        <v>50.54</v>
+        <v>27.94</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.794</v>
+        <v>0.163</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2.702</v>
+        <v>0.199</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2246,28 +2246,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.905</v>
+        <v>0.66</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-0.0622</v>
+        <v>-0.0833</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1778100</v>
+        <v>3056300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="H40" t="n">
-        <v>46.41</v>
+        <v>50.46</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.956</v>
+        <v>0.671</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.826</v>
+        <v>0.61</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2291,39 +2291,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.14</v>
+        <v>0.435</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1716100</v>
+        <v>3051600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="H41" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.43</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.161</v>
+        <v>0.45</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.122</v>
+        <v>0.428</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2336,28 +2336,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.425</v>
+        <v>4.95</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-0.0659</v>
+        <v>-0.0275</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1654700</v>
+        <v>3048100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="H42" t="n">
-        <v>51.32</v>
+        <v>53.85</v>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.426</v>
+        <v>4.928</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.413</v>
+        <v>4.668</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2381,28 +2381,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0109</v>
+        <v>1.02</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.0467</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1589600</v>
+        <v>2997300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H43" t="n">
-        <v>56.18</v>
+        <v>43.05</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.606</v>
+        <v>1.067</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.785</v>
+        <v>1.038</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2426,28 +2426,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.77</v>
+        <v>0.28</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.0375</v>
+        <v>-0.0508</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1526700</v>
+        <v>2886500</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="H44" t="n">
-        <v>48.13</v>
+        <v>49.81</v>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.779</v>
+        <v>0.278</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.773</v>
+        <v>0.302</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2471,39 +2471,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4.98</v>
+        <v>1.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-0.0216</v>
+        <v>-0.0449</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1472500</v>
+        <v>2829900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.06</v>
+        <v>0.57</v>
       </c>
       <c r="H45" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.66</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4.931</v>
+        <v>1.749</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4.668</v>
+        <v>1.777</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2516,28 +2516,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.36</v>
+        <v>1.27</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.0649</v>
+        <v>-0.1477</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1452200</v>
+        <v>2789900</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.17</v>
+        <v>1.58</v>
       </c>
       <c r="H46" t="n">
-        <v>55.44</v>
+        <v>20.15</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.355</v>
+        <v>1.486</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.323</v>
+        <v>1.611</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2561,28 +2561,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>-0.08699999999999999</v>
+        <v>3.69</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1432300</v>
+        <v>2755500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="H47" t="n">
-        <v>26.33</v>
+        <v>55.97</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.358</v>
+        <v>3.605</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.382</v>
+        <v>2.785</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2606,28 +2606,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.06</v>
+        <v>2.77</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-0.0463</v>
+        <v>-0.0281</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1429600</v>
+        <v>2742000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H48" t="n">
-        <v>36.34</v>
+        <v>49.79</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.211</v>
+        <v>2.793</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.216</v>
+        <v>2.702</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2651,28 +2651,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.0165</v>
+        <v>0.765</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.08380000000000001</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1414500</v>
+        <v>2508000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H49" t="n">
-        <v>38.27</v>
+        <v>56.18</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.615</v>
+        <v>0.752</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>7.725</v>
+        <v>0.667</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2696,28 +2696,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.975</v>
+        <v>0.415</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-0.0347</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1400300</v>
+        <v>2454500</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H50" t="n">
-        <v>81.42</v>
+        <v>48.81</v>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.493</v>
+        <v>0.413</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2750,19 +2750,19 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.0015</v>
+        <v>6.55</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1335200</v>
+        <v>2393800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="H51" t="n">
-        <v>66.38</v>
+        <v>61.56</v>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5.93</v>
+        <v>5.907</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>5.807</v>
+        <v>5.802</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2786,39 +2786,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.385</v>
+        <v>2.06</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>-0.04940000000000001</v>
+        <v>-0.0463</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1332200</v>
+        <v>2207000</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="H52" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.34</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.386</v>
+        <v>2.211</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.391</v>
+        <v>2.216</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2831,39 +2831,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.76</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1330000</v>
+        <v>2192300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="H53" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.774</v>
+        <v>0.778</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2876,39 +2876,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.28</v>
+        <v>0.38</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0617</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1319600</v>
+        <v>2191800</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.13</v>
+        <v>1.07</v>
       </c>
       <c r="H54" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.48</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.319</v>
+        <v>0.386</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.308</v>
+        <v>0.391</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2921,39 +2921,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.1622</v>
+        <v>2.6</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1272900</v>
+        <v>2161400</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.16</v>
+        <v>0.35</v>
       </c>
       <c r="H55" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.02</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.186</v>
+        <v>2.626</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.183</v>
+        <v>2.585</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2966,28 +2966,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.47</v>
+        <v>1.26</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.0803</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1252600</v>
+        <v>2110900</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.17</v>
+        <v>0.7</v>
       </c>
       <c r="H56" t="n">
-        <v>27.33</v>
+        <v>57.33</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.52</v>
+        <v>1.239</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.569</v>
+        <v>1.017</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3011,39 +3011,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-0.0296</v>
+        <v>4.68</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1201100</v>
+        <v>2075100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H57" t="n">
-        <v>50.48</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.18</v>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.628</v>
+        <v>4.718</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.586</v>
+        <v>4.884</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3056,28 +3056,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0678</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1175000</v>
+        <v>2063600</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.21</v>
+        <v>0.59</v>
       </c>
       <c r="H58" t="n">
-        <v>56.86</v>
+        <v>51.7</v>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.551</v>
+        <v>5.48</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.497</v>
+        <v>5.366</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3101,28 +3101,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.4</v>
+        <v>0.315</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.0123</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1134000</v>
+        <v>1989800</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.74</v>
+        <v>0.44</v>
       </c>
       <c r="H59" t="n">
-        <v>32.46</v>
+        <v>26.33</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.42</v>
+        <v>0.358</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.439</v>
+        <v>0.382</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3146,39 +3146,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.785</v>
+        <v>0.925</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.0599</v>
+        <v>-0.0842</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1104200</v>
+        <v>1973000</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="H60" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.754</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.667</v>
+        <v>0.492</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3191,39 +3191,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.19</v>
+        <v>0.595</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.048</v>
+        <v>-0.0775</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1090400</v>
+        <v>1940500</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="H61" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.276</v>
+        <v>0.596</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.378</v>
+        <v>0.582</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3236,28 +3236,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.61</v>
+        <v>1.61</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0062</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1080200</v>
+        <v>1938600</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H62" t="n">
-        <v>54.31</v>
+        <v>37.52</v>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.598</v>
+        <v>1.664</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.583</v>
+        <v>1.779</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3281,39 +3281,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.515</v>
+        <v>2.74</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.0636</v>
+        <v>-0.0712</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>991600</v>
+        <v>1922500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="H63" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.45</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.481</v>
+        <v>2.953</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.454</v>
+        <v>3.03</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3326,28 +3326,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2.82</v>
+        <v>5.4</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0441</v>
+        <v>-0.0526</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>931300</v>
+        <v>1921200</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="H64" t="n">
-        <v>37.55</v>
+        <v>43.55</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.961</v>
+        <v>5.622</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>3.031</v>
+        <v>5.333</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3371,39 +3371,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>5.56</v>
+        <v>0.425</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0576</v>
+        <v>-0.0761</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>912500</v>
+        <v>1848800</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="H65" t="n">
-        <v>53.14</v>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.9</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>5.485</v>
+        <v>0.455</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>5.367</v>
+        <v>0.422</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3416,39 +3416,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.0323</v>
+        <v>-0.0174</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>895000</v>
+        <v>1847700</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.46</v>
+        <v>0.19</v>
       </c>
       <c r="H66" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.97</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.716</v>
+        <v>1.16</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.694</v>
+        <v>1.121</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3461,28 +3461,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.0902</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>893500</v>
+        <v>1768800</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="H67" t="n">
-        <v>60.87</v>
+        <v>55.52</v>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.03</v>
+        <v>0.551</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.869</v>
+        <v>0.497</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3506,39 +3506,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0614</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>868600</v>
+        <v>1767900</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="H68" t="n">
-        <v>43.89</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.343</v>
+        <v>1.071</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.244</v>
+        <v>0.925</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3551,39 +3551,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.0102</v>
+        <v>0.355</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.0779</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>858100</v>
+        <v>1744500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="H69" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.3</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>3.873</v>
+        <v>0.354</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3.592</v>
+        <v>0.323</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3596,39 +3596,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>4.69</v>
+        <v>0.295</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>845700</v>
+        <v>1726000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.05</v>
+        <v>0.59</v>
       </c>
       <c r="H70" t="n">
-        <v>44.19</v>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>4.719</v>
+        <v>0.295</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4.884</v>
+        <v>0.296</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3641,39 +3641,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.79</v>
+        <v>1.28</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.0247</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>840400</v>
+        <v>1696600</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="H71" t="n">
-        <v>55.47</v>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.38</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.771</v>
+        <v>1.319</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.716</v>
+        <v>1.308</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3686,36 +3686,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0159</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>831300</v>
+        <v>1643800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="H72" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.638</v>
+        <v>0.613</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0.612</v>
@@ -3731,39 +3731,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.025</v>
+        <v>0.21</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>0.1351</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>820600</v>
+        <v>1610900</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.34</v>
+        <v>1.47</v>
       </c>
       <c r="H73" t="n">
-        <v>35.84</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.78</v>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.614</v>
+        <v>0.185</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.634</v>
+        <v>0.183</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3776,28 +3776,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.77</v>
+        <v>0.475</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>-0.0314</v>
+        <v>-0.05</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>786100</v>
+        <v>1495700</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H74" t="n">
-        <v>59.05</v>
+        <v>28.32</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.739</v>
+        <v>0.52</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.656</v>
+        <v>0.569</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3821,28 +3821,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>3.29</v>
+        <v>2.66</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>-0.0179</v>
+        <v>-0.0796</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>778600</v>
+        <v>1447400</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H75" t="n">
-        <v>32.99</v>
+        <v>37.97</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>3.451</v>
+        <v>2.938</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>3.645</v>
+        <v>2.831</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3866,28 +3866,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2.8</v>
+        <v>1.16</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.021</v>
+        <v>-0.0333</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>776500</v>
+        <v>1440800</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="H76" t="n">
-        <v>53.68</v>
+        <v>54.32</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.78</v>
+        <v>1.155</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.611</v>
+        <v>1.073</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3911,28 +3911,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>2.98</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0688</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>769500</v>
+        <v>1412200</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="H77" t="n">
-        <v>45.98</v>
+        <v>51.48</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>4.366</v>
+        <v>2.999</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>4.458</v>
+        <v>2.812</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3956,40 +3956,36 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.535</v>
+        <v>0.455</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.0183</v>
+        <v>-0.0319</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>766000</v>
+        <v>1363300</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H78" t="n">
-        <v>31.42</v>
+        <v>33.62</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>0.62</v>
-      </c>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
     </row>
@@ -4001,39 +3997,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.62</v>
+        <v>2.75</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0385</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>765900</v>
+        <v>1357800</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="H79" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.77</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.613</v>
+        <v>2.775</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.612</v>
+        <v>2.61</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4046,28 +4042,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>10.98</v>
+        <v>0.745</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>-0.0018</v>
+        <v>-0.0387</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>727400</v>
+        <v>1353300</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.21</v>
+        <v>0.7</v>
       </c>
       <c r="H80" t="n">
-        <v>72.66</v>
+        <v>57.1</v>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
@@ -4075,10 +4071,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>10.305</v>
+        <v>0.716</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>9.561</v>
+        <v>0.694</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4091,28 +4087,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0.0194</v>
+        <v>4.03</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.0495</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>718100</v>
+        <v>1348900</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H81" t="n">
-        <v>46.16</v>
+        <v>55.83</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4120,10 +4116,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>10.02</v>
+        <v>3.971</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>10.203</v>
+        <v>3.463</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4136,39 +4132,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2.94</v>
+        <v>1.19</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.0034</v>
+        <v>-0.048</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>716200</v>
+        <v>1347600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H82" t="n">
-        <v>77.43000000000001</v>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.7</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.675</v>
+        <v>1.276</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2.31</v>
+        <v>1.378</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4181,39 +4177,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>5.42</v>
+        <v>0.385</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.0491</v>
+        <v>-0.0723</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>716000</v>
+        <v>1331900</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H83" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.53</v>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>5.624</v>
+        <v>0.386</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>5.334</v>
+        <v>0.375</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4226,39 +4222,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4.09</v>
+        <v>0.25</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>-0.0354</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>709000</v>
+        <v>1325200</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.08</v>
+        <v>0.6</v>
       </c>
       <c r="H84" t="n">
-        <v>58.06</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.83</v>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>3.977</v>
+        <v>0.25</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3.465</v>
+        <v>0.254</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4271,39 +4267,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.27</v>
+        <v>0.395</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.073</v>
+        <v>-0.0247</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>682600</v>
+        <v>1304000</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.19</v>
+        <v>0.85</v>
       </c>
       <c r="H85" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.4</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.293</v>
+        <v>0.419</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.201</v>
+        <v>0.439</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4316,39 +4312,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.7</v>
+        <v>1.07</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.0541</v>
+        <v>-0.123</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>671600</v>
+        <v>1289800</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="H86" t="n">
-        <v>39.37</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.94</v>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.755</v>
+        <v>1.026</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.747</v>
+        <v>0.868</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4361,39 +4357,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.73</v>
+        <v>3.85</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>-0.0554</v>
+        <v>-0.0204</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>661900</v>
+        <v>1275800</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="H87" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.45</v>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.944</v>
+        <v>3.862</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.832</v>
+        <v>3.589</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4406,39 +4402,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E88" s="9" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>643800</v>
+        <v>1265100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H88" t="n">
-        <v>57.41</v>
-      </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.9</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.999</v>
+        <v>0.301</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.981</v>
+        <v>0.298</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4451,39 +4447,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.0278</v>
+        <v>0.63</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.137</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>641600</v>
+        <v>1258300</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>53.16</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.19</v>
+        <v>0.532</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.133</v>
+        <v>0.448</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4496,28 +4492,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>-0.028</v>
+        <v>-0.0435</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>632800</v>
+        <v>1252300</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.37</v>
+        <v>0.53</v>
       </c>
       <c r="H90" t="n">
-        <v>41.57</v>
+        <v>70.23</v>
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
@@ -4525,10 +4521,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.058</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.19</v>
+        <v>0.626</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4541,39 +4537,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.775</v>
+        <v>0.265</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.0373</v>
+        <v>-0.0536</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>629100</v>
+        <v>1251100</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="H91" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.67</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.771</v>
+        <v>0.287</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.762</v>
+        <v>0.306</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4586,28 +4582,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.2</v>
+        <v>0.615</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0315</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>619200</v>
+        <v>1247900</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
       <c r="H92" t="n">
-        <v>42.7</v>
+        <v>41.62</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4615,10 +4611,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.267</v>
+        <v>0.636</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.316</v>
+        <v>0.612</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4631,28 +4627,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>-0.0278</v>
+        <v>4.31</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>615900</v>
+        <v>1228000</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H93" t="n">
-        <v>21.62</v>
+        <v>46.4</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4660,10 +4656,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.95</v>
+        <v>4.367</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.99</v>
+        <v>4.458</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4676,28 +4672,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.31</v>
+        <v>0.785</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-0.0576</v>
+        <v>-0.0309</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>613500</v>
+        <v>1182200</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="H94" t="n">
-        <v>61.24</v>
+        <v>54.63</v>
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
@@ -4705,10 +4701,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.228</v>
+        <v>0.77</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.156</v>
+        <v>0.715</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4721,28 +4717,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.895</v>
+        <v>1.05</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0272</v>
+        <v>-0.0541</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>602500</v>
+        <v>1160000</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="H95" t="n">
-        <v>48.65</v>
+        <v>54.03</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4750,10 +4746,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.906</v>
+        <v>1.056</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.864</v>
+        <v>0.901</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4766,39 +4762,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>-0.0472</v>
+        <v>0.62</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>598400</v>
+        <v>1151000</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H96" t="n">
-        <v>55.99</v>
-      </c>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.492</v>
+        <v>0.613</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.48</v>
+        <v>0.599</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4811,28 +4807,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.835</v>
+        <v>0.775</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>-0.07730000000000001</v>
+        <v>-0.0373</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>590200</v>
+        <v>1127800</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>53.89</v>
+        <v>51.66</v>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
@@ -4840,7 +4836,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.827</v>
+        <v>0.771</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0.762</v>
@@ -4856,28 +4852,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E98" s="9" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.0314</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>588700</v>
+        <v>1108300</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="H98" t="n">
-        <v>72.15000000000001</v>
+        <v>59.05</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4885,10 +4881,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.249</v>
+        <v>0.739</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1.019</v>
+        <v>0.656</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4901,39 +4897,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.79</v>
+        <v>1.3</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0299</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>562000</v>
+        <v>1077000</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="H99" t="n">
-        <v>76.04000000000001</v>
-      </c>
-      <c r="I99" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.17</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>1.345</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.626</v>
+        <v>1.245</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4946,39 +4942,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.0351</v>
+        <v>10.02</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>544700</v>
+        <v>1069600</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H100" t="n">
-        <v>59</v>
-      </c>
-      <c r="I100" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.36</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.074</v>
+        <v>10.022</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.926</v>
+        <v>10.203</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4991,39 +4987,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.65</v>
+        <v>0.455</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.1096</v>
+        <v>-0.0421</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>524500</v>
+        <v>1059700</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H101" t="n">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.6</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.534</v>
+        <v>0.46</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.449</v>
+        <v>0.461</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5036,28 +5032,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>3.08</v>
+        <v>0.5</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.0375</v>
+        <v>-0.0566</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>509300</v>
+        <v>1054700</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="H102" t="n">
-        <v>55.74</v>
+        <v>54.23</v>
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
@@ -5065,16 +5061,1584 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>3.008</v>
+        <v>0.492</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.814</v>
+        <v>0.48</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>1052100</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H103" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>1048500</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H104" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>1038300</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H105" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>10.294</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>9.558999999999999</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.0545</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>1032400</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H106" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>1031500</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>7.573</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0475</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GBBOND</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>1004500</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n"/>
+      <c r="K108" s="2" t="n"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0608</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>997200</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H109" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.07190000000000001</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>976400</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H110" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.0557</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>941800</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H111" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>3.182</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>3.379</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>-0.0803</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>925400</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H112" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>-0.07730000000000001</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>908100</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H113" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>900700</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.0278</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>879700</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H115" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>0.03240000000000001</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>876500</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H116" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>2.191</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>871400</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H117" t="n">
+        <v>32</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>3.449</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>3.644</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>858800</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H118" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>8.712999999999999</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.1024</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>842800</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H119" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>817900</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H120" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.07629999999999999</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>810500</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H121" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>780700</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H122" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>2.462</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>766000</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.0302</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>717100</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H124" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>7.289</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H125" t="n">
+        <v>52.57</v>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0288</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>648900</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>648800</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H127" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>646900</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H128" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.0565</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>646400</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H129" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="E130" s="9" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>621700</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H130" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>6.454</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>614000</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H131" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>539900</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H132" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>5.045</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>5.058</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>-0.004699999999999999</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>539000</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H133" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.0694</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>528400</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H134" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>525700</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H135" t="n">
+        <v>65.39</v>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>2.072</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>510400</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H136" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>4.327</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>4.358</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.0424</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>509900</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H137" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M102"/>
+  <autoFilter ref="A1:M137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
+++ b/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-13" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,8 +82,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.1389</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>59608500</v>
+        <v>64542300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="H2" t="n">
         <v>48.11</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.1176</v>
+        <v>-0.1765</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>50800800</v>
+        <v>56442400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H3" t="n">
-        <v>22.65</v>
+        <v>22.22</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.385</v>
@@ -648,10 +648,10 @@
         <v>-0.07690000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>28342300</v>
+        <v>36169100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.88</v>
+        <v>1.12</v>
       </c>
       <c r="H4" t="n">
         <v>48.22</v>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-0.075</v>
+        <v>0.845</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>20042300</v>
+        <v>29413500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.87</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.56</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.195</v>
+        <v>0.788</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.184</v>
+        <v>0.714</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-0.0435</v>
+        <v>0.39</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19256800</v>
+        <v>24379200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.32</v>
+        <v>0.66</v>
       </c>
       <c r="H6" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+        <v>70.36</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.284</v>
+        <v>0.361</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.247</v>
+        <v>0.243</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.83</v>
+        <v>0.325</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.0178</v>
+        <v>-0.058</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17623700</v>
+        <v>22004700</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="H7" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
+        <v>68.2</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.787</v>
+        <v>0.283</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.714</v>
+        <v>0.246</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.0128</v>
+        <v>0.18</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14638000</v>
+        <v>20479300</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.4</v>
+        <v>0.89</v>
       </c>
       <c r="H8" t="n">
-        <v>71.42</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.31</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.361</v>
+        <v>0.195</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.243</v>
+        <v>0.184</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -867,27 +867,27 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.0142</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12862400</v>
+        <v>16209800</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="H9" t="n">
-        <v>75.53</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.848</v>
+        <v>1.851</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>1.658</v>
@@ -903,39 +903,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.415</v>
+        <v>0.575</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.1075</v>
+        <v>-0.0873</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>12547100</v>
+        <v>13402700</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>3.68</v>
+        <v>0.74</v>
       </c>
       <c r="H10" t="n">
-        <v>62.54</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
+        <v>51.64</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.364</v>
+        <v>0.58</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.35</v>
+        <v>0.522</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,33 +948,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.1183</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10628100</v>
+        <v>13154500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
+        <v>3.86</v>
+      </c>
+      <c r="H11" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.35</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,40 +993,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-0.0873</v>
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9778200</v>
+        <v>11550800</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H12" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+        <v>0.33</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.522</v>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1031,28 +1031,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.105</v>
+        <v>1.5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.0455</v>
+        <v>-0.2021</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8715900</v>
+        <v>9288600</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>37.13</v>
+        <v>21.07</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.114</v>
+        <v>1.861</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.122</v>
+        <v>2.013</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0207</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MESTRON</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0.2</v>
+        <v>0.105</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8348200</v>
+        <v>9182100</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.79</v>
+        <v>1.39</v>
       </c>
       <c r="H14" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.13</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.092</v>
+        <v>0.122</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.0263</v>
+        <v>0.19</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8106800</v>
+        <v>8878800</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>10.55</v>
+        <v>11.55</v>
       </c>
       <c r="H15" t="n">
-        <v>58.36</v>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
+        <v>54.59</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.48</v>
+        <v>0.62</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.2128</v>
+        <v>-0.008</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7752600</v>
+        <v>8817600</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2</v>
+        <v>0.34</v>
       </c>
       <c r="H16" t="n">
-        <v>20.51</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.95999999999999</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.859</v>
+        <v>0.586</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2.013</v>
+        <v>0.51</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,39 +1211,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0207</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>MESTRON</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.0345</v>
+        <v>0.09</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7683400</v>
+        <v>8692500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.3</v>
+        <v>2.91</v>
       </c>
       <c r="H17" t="n">
-        <v>42.91</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.2</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.154</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.148</v>
+        <v>0.092</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.62</v>
+        <v>0.14</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.0345</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6871600</v>
+        <v>8396900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H18" t="n">
-        <v>68.95999999999999</v>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.91</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.586</v>
+        <v>0.154</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.51</v>
+        <v>0.148</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.355</v>
+        <v>2.74</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-0.0139</v>
+        <v>-0.0108</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6462900</v>
+        <v>8351800</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="H19" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
+        <v>61.19</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.345</v>
+        <v>2.636</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.326</v>
+        <v>2.509</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.45</v>
+        <v>0.355</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.0139</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6219800</v>
+        <v>8095800</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.16</v>
+        <v>1.07</v>
       </c>
       <c r="H20" t="n">
-        <v>24.17</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.54</v>
+        <v>0.345</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.737</v>
+        <v>0.326</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,39 +1391,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.675</v>
+        <v>0.425</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.08779999999999999</v>
+        <v>-0.023</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5918200</v>
+        <v>6896800</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.7</v>
+        <v>0.29</v>
       </c>
       <c r="H21" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.56</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.71</v>
+        <v>0.675</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-0.0217</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5856400</v>
+        <v>6881900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="H22" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.62</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.634</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.508</v>
+        <v>0.68</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1481,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.495</v>
+        <v>0.865</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.0833</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5162700</v>
+        <v>6755700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="H23" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.92</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.52</v>
+        <v>0.868</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.53</v>
+        <v>0.869</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0.0204</v>
+        <v>0.445</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.06320000000000001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4980200</v>
+        <v>6750100</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>3.08</v>
+        <v>0.18</v>
       </c>
       <c r="H24" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.73</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.238</v>
+        <v>0.539</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.243</v>
+        <v>0.737</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,39 +1571,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.0667</v>
+        <v>0.39</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4596600</v>
+        <v>6411700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="H25" t="n">
-        <v>75.65000000000001</v>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.82</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.293</v>
+        <v>0.401</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.276</v>
+        <v>0.409</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,39 +1616,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.865</v>
+        <v>4.91</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0354</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4479700</v>
+        <v>6185400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H26" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
+        <v>51.93</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.868</v>
+        <v>4.924</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.869</v>
+        <v>4.667</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,39 +1661,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-0.08960000000000001</v>
+        <v>0.82</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4325100</v>
+        <v>6057100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="H27" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.324</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.338</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,39 +1706,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.82</v>
+        <v>0.775</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4102100</v>
+        <v>5785600</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="H28" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
+        <v>50.45</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.774</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1751,28 +1751,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>0026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SMRT</t>
+          <t>NOVAMSC</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.1111</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3970900</v>
+        <v>5652300</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.21</v>
+        <v>11.74</v>
       </c>
       <c r="H29" t="n">
-        <v>28.91</v>
+        <v>36.58</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.184</v>
+        <v>0.057</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.194</v>
+        <v>0.062</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,39 +1796,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-0.0345</v>
+        <v>0.25</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3881500</v>
+        <v>5612200</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.16</v>
+        <v>3.47</v>
       </c>
       <c r="H30" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
+        <v>58.46</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.411</v>
+        <v>0.238</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.35</v>
+        <v>0.243</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1841,28 +1841,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.0127</v>
+        <v>-0.0741</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3824400</v>
+        <v>5493200</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="H31" t="n">
-        <v>33.82</v>
+        <v>43.62</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.401</v>
+        <v>0.52</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.409</v>
+        <v>0.53</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1886,39 +1886,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0.0095</v>
+        <v>0.045</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.125</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3820500</v>
+        <v>5430500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.24</v>
+        <v>2.83</v>
       </c>
       <c r="H32" t="n">
-        <v>56.81</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.63</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.513</v>
+        <v>0.042</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.44</v>
+        <v>0.047</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1931,39 +1931,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>-0.1376</v>
+        <v>0.315</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.05</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3759600</v>
+        <v>5229200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="H33" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.67</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.58</v>
+        <v>0.292</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.637</v>
+        <v>0.276</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1976,39 +1976,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.465</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.1468</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3522000</v>
+        <v>4990700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.24</v>
+        <v>0.9</v>
       </c>
       <c r="H34" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.66</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.774</v>
+        <v>0.58</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.775</v>
+        <v>0.637</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2021,28 +2021,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.215</v>
+        <v>0.305</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.0444</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3520600</v>
+        <v>4981900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.14</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="n">
-        <v>30.21</v>
+        <v>40.78</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.246</v>
+        <v>0.324</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.301</v>
+        <v>0.338</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2066,28 +2066,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.275</v>
+        <v>0.155</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.0833</v>
+        <v>-0.1389</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3390700</v>
+        <v>4638700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.28</v>
+        <v>1.41</v>
       </c>
       <c r="H36" t="n">
-        <v>45.58</v>
+        <v>26.85</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.29</v>
+        <v>0.183</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.281</v>
+        <v>0.193</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2111,28 +2111,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.07769999999999999</v>
+        <v>-0.0187</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3333700</v>
+        <v>4613100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="H37" t="n">
-        <v>44.62</v>
+        <v>47.22</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.954</v>
+        <v>1.07</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.825</v>
+        <v>1.038</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2165,19 +2165,19 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0.0207</v>
+        <v>7.4</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0193</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3317500</v>
+        <v>4426700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="H38" t="n">
-        <v>39.76</v>
+        <v>39.27</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.618</v>
+        <v>7.617</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>7.725</v>
@@ -2201,28 +2201,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.145</v>
+        <v>2.77</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-0.0333</v>
+        <v>-0.0281</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3187900</v>
+        <v>4392800</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="H39" t="n">
-        <v>27.94</v>
+        <v>49.79</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.163</v>
+        <v>2.793</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.199</v>
+        <v>2.702</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2246,28 +2246,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.66</v>
+        <v>0.275</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>-0.0833</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3056300</v>
+        <v>4135900</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0.34</v>
       </c>
       <c r="H40" t="n">
-        <v>50.46</v>
+        <v>45.58</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.671</v>
+        <v>0.29</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.61</v>
+        <v>0.281</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2291,39 +2291,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.435</v>
+        <v>1.29</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0584</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3051600</v>
+        <v>4016900</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.29</v>
+        <v>1.32</v>
       </c>
       <c r="H41" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.73</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.45</v>
+        <v>1.242</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.428</v>
+        <v>1.018</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2336,39 +2336,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4.95</v>
+        <v>0.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-0.0275</v>
+        <v>-0.0674</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3048100</v>
+        <v>3988100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="H42" t="n">
-        <v>53.85</v>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.928</v>
+        <v>0.955</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.668</v>
+        <v>0.826</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2381,28 +2381,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.0467</v>
+        <v>-0.0506</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2997300</v>
+        <v>3948000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.24</v>
+        <v>0.79</v>
       </c>
       <c r="H43" t="n">
-        <v>43.05</v>
+        <v>41.62</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.067</v>
+        <v>1.748</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.038</v>
+        <v>1.777</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2426,39 +2426,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.28</v>
+        <v>0.655</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.0508</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2886500</v>
+        <v>3937000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="H44" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.61</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.278</v>
+        <v>0.67</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.302</v>
+        <v>0.61</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2471,28 +2471,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-0.0449</v>
+        <v>0.53</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2829900</v>
+        <v>3928500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.57</v>
+        <v>0.24</v>
       </c>
       <c r="H45" t="n">
-        <v>42.66</v>
+        <v>56.81</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.749</v>
+        <v>0.513</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.777</v>
+        <v>0.44</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2516,28 +2516,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.27</v>
+        <v>0.215</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.1477</v>
+        <v>-0.0444</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2789900</v>
+        <v>3674800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.58</v>
+        <v>0.14</v>
       </c>
       <c r="H46" t="n">
-        <v>20.15</v>
+        <v>30.21</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.486</v>
+        <v>0.246</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.611</v>
+        <v>0.301</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2561,39 +2561,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.28</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.0508</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2755500</v>
+        <v>3641700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="H47" t="n">
-        <v>55.97</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.81</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3.605</v>
+        <v>0.278</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.785</v>
+        <v>0.302</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2606,28 +2606,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.77</v>
+        <v>0.145</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-0.0281</v>
+        <v>-0.0333</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2742000</v>
+        <v>3574100</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H48" t="n">
-        <v>49.79</v>
+        <v>27.94</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.793</v>
+        <v>0.163</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.702</v>
+        <v>0.199</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2651,28 +2651,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.765</v>
+        <v>1.28</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-0.08380000000000001</v>
+        <v>-0.1409</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2508000</v>
+        <v>3554900</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.38</v>
+        <v>2.02</v>
       </c>
       <c r="H49" t="n">
-        <v>56.18</v>
+        <v>20.62</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.752</v>
+        <v>1.487</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.667</v>
+        <v>1.611</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2696,39 +2696,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.415</v>
+        <v>2.07</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.0417</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2454500</v>
+        <v>3535000</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H50" t="n">
-        <v>48.81</v>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.93</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.425</v>
+        <v>2.212</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.413</v>
+        <v>2.216</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2741,39 +2741,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>6.55</v>
+        <v>0.425</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-0.0339</v>
+        <v>-0.0761</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2393800</v>
+        <v>3294300</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.49</v>
+        <v>0.91</v>
       </c>
       <c r="H51" t="n">
-        <v>61.56</v>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.9</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5.907</v>
+        <v>0.455</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>5.802</v>
+        <v>0.422</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2786,40 +2786,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2.06</v>
+        <v>0.1</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>-0.0463</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2207000</v>
+        <v>3274100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H52" t="n">
-        <v>36.34</v>
+        <v>0.21</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n">
-        <v>2.211</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>2.216</v>
-      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
     </row>
@@ -2831,39 +2824,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2192300</v>
+        <v>3203500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="H53" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.39</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.778</v>
+        <v>0.449</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.773</v>
+        <v>0.428</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2876,39 +2869,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>-0.0617</v>
+        <v>0.315</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2191800</v>
+        <v>3173200</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1.07</v>
+        <v>0.17</v>
       </c>
       <c r="H54" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
+        <v>61.95</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.386</v>
+        <v>0.307</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.391</v>
+        <v>0.296</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2921,39 +2914,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2.6</v>
+        <v>6.62</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2161400</v>
+        <v>3070600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H55" t="n">
-        <v>49.02</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.92</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.626</v>
+        <v>5.914</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.585</v>
+        <v>5.804</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2966,28 +2959,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.0803</v>
+        <v>3.67</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2110900</v>
+        <v>3019300</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="H56" t="n">
-        <v>57.33</v>
+        <v>55.54</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2995,10 +2988,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.239</v>
+        <v>3.603</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.017</v>
+        <v>2.784</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3011,39 +3004,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>0.0241</v>
+        <v>0.48</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2075100</v>
+        <v>2966300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="H57" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.38</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4.718</v>
+        <v>0.52</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>4.884</v>
+        <v>0.569</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3056,39 +3049,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>-0.0678</v>
+        <v>-0.0596</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2063600</v>
+        <v>2917000</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.59</v>
+        <v>0.21</v>
       </c>
       <c r="H58" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.39</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5.48</v>
+        <v>5.618</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>5.366</v>
+        <v>5.333</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3101,28 +3094,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1989800</v>
+        <v>2878300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.44</v>
+        <v>0.99</v>
       </c>
       <c r="H59" t="n">
-        <v>26.33</v>
+        <v>49.15</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3130,10 +3123,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.358</v>
+        <v>0.295</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.382</v>
+        <v>0.296</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3146,39 +3139,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.925</v>
+        <v>0.8</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.0842</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1973000</v>
+        <v>2870000</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.57</v>
+        <v>0.44</v>
       </c>
       <c r="H60" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.71</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.755</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.492</v>
+        <v>0.668</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3191,39 +3184,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.595</v>
+        <v>0.415</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.0775</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1940500</v>
+        <v>2825100</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="H61" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
+        <v>48.81</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.596</v>
+        <v>0.425</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.582</v>
+        <v>0.413</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3236,39 +3229,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.61</v>
+        <v>4.03</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.0495</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1938600</v>
+        <v>2722300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H62" t="n">
-        <v>37.52</v>
-      </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.83</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.664</v>
+        <v>3.971</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.779</v>
+        <v>3.463</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3281,39 +3274,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2.74</v>
+        <v>5.49</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.0712</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1922500</v>
+        <v>2705700</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H63" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.47</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.953</v>
+        <v>5.479</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3.03</v>
+        <v>5.366</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3326,28 +3319,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1921200</v>
+        <v>2701100</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="H64" t="n">
-        <v>43.55</v>
+        <v>49.02</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3355,10 +3348,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5.622</v>
+        <v>2.626</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>5.333</v>
+        <v>2.585</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3371,28 +3364,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.425</v>
+        <v>0.765</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0761</v>
+        <v>-0.0438</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1848800</v>
+        <v>2557700</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="H65" t="n">
-        <v>41.9</v>
+        <v>46.94</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3400,10 +3393,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.455</v>
+        <v>0.778</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.422</v>
+        <v>0.773</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3416,39 +3409,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.13</v>
+        <v>0.385</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.0174</v>
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1847700</v>
+        <v>2546400</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.19</v>
+        <v>1.24</v>
       </c>
       <c r="H66" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.26</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.16</v>
+        <v>0.386</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.121</v>
+        <v>0.391</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3461,39 +3454,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.07440000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1768800</v>
+        <v>2545300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="H67" t="n">
-        <v>55.52</v>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
+        <v>53.12</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.551</v>
+        <v>0.597</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.497</v>
+        <v>0.583</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3506,39 +3499,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>-0.0614</v>
+        <v>1.15</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1767900</v>
+        <v>2489800</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="H68" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.32</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.071</v>
+        <v>1.162</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.925</v>
+        <v>1.122</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3551,28 +3544,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.355</v>
+        <v>0.315</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.0779</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1744500</v>
+        <v>2430500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="H69" t="n">
-        <v>53.3</v>
+        <v>26.33</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3580,10 +3573,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.323</v>
+        <v>0.382</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3596,39 +3589,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>2.79</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.0245</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1726000</v>
+        <v>2419500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.59</v>
+        <v>0.26</v>
       </c>
       <c r="H70" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.07</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.295</v>
+        <v>2.779</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.296</v>
+        <v>2.611</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3641,39 +3634,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0062</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1696600</v>
+        <v>2396000</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H71" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.52</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.319</v>
+        <v>1.664</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.308</v>
+        <v>1.779</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3686,39 +3679,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0159</v>
+        <v>4.69</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1643800</v>
+        <v>2368600</v>
       </c>
       <c r="G72" s="5" t="n">
         <v>0.15</v>
       </c>
       <c r="H72" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
+        <v>44.19</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.613</v>
+        <v>4.719</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.612</v>
+        <v>4.884</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3731,39 +3724,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E73" s="9" t="n">
-        <v>0.1351</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.07440000000000001</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1610900</v>
+        <v>2341400</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1.47</v>
+        <v>0.43</v>
       </c>
       <c r="H73" t="n">
-        <v>68.78</v>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
+        <v>55.52</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.185</v>
+        <v>0.551</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.183</v>
+        <v>0.497</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3776,28 +3769,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.475</v>
+        <v>1.28</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1495700</v>
+        <v>2297400</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H74" t="n">
-        <v>28.32</v>
+        <v>43.38</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3805,10 +3798,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.52</v>
+        <v>1.319</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.569</v>
+        <v>1.308</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3821,28 +3814,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>-0.0796</v>
+        <v>-0.061</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1447400</v>
+        <v>2294900</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="H75" t="n">
-        <v>37.97</v>
+        <v>34.88</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3850,10 +3843,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.938</v>
+        <v>2.956</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.831</v>
+        <v>3.03</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3866,39 +3859,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.0333</v>
+        <v>-0.0526</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1440800</v>
+        <v>2153200</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="H76" t="n">
-        <v>54.32</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.63</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.155</v>
+        <v>1.072</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.073</v>
+        <v>0.925</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3911,39 +3904,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>-0.0688</v>
+        <v>-0.0693</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1412200</v>
+        <v>2149600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="H77" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.73999999999999</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.812</v>
+        <v>0.493</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3956,36 +3949,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.455</v>
+        <v>1.18</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.0319</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1363300</v>
+        <v>2140500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H78" t="n">
-        <v>33.62</v>
+        <v>27.69</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="n"/>
+      <c r="J78" s="2" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1.378</v>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
     </row>
@@ -3997,28 +3994,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>-0.0385</v>
+        <v>7.28</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1357800</v>
+        <v>2126600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="H79" t="n">
-        <v>50.77</v>
+        <v>29.22</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4026,10 +4023,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.775</v>
+        <v>7.574</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2.61</v>
+        <v>8.071</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4042,39 +4039,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.745</v>
+        <v>0.45</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>-0.0387</v>
+        <v>-0.0526</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1353300</v>
+        <v>2118200</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="H80" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.95</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.716</v>
+        <v>0.46</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.694</v>
+        <v>0.461</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4087,39 +4084,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>4.03</v>
+        <v>0.78</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>-0.0495</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1348900</v>
+        <v>2014100</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H81" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.81</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>3.971</v>
+        <v>0.77</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>3.463</v>
+        <v>0.715</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4132,28 +4129,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.19</v>
+        <v>0.355</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.048</v>
+        <v>-0.0779</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1347600</v>
+        <v>1930500</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H82" t="n">
-        <v>28.7</v>
+        <v>53.3</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4161,10 +4158,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.276</v>
+        <v>0.354</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1.378</v>
+        <v>0.323</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4177,39 +4174,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.385</v>
+        <v>2.93</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.0723</v>
+        <v>-0.0068</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1331900</v>
+        <v>1885500</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.11</v>
+        <v>0.58</v>
       </c>
       <c r="H83" t="n">
-        <v>50.53</v>
-      </c>
-      <c r="I83" s="8" t="inlineStr">
+        <v>76.3</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.386</v>
+        <v>2.674</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.375</v>
+        <v>2.309</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4222,39 +4219,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.25</v>
+        <v>0.635</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1301</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1325200</v>
+        <v>1877800</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.6</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>49.83</v>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
+        <v>66.91</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.25</v>
+        <v>0.532</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.254</v>
+        <v>0.448</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4267,28 +4264,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.395</v>
+        <v>2.71</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.0247</v>
+        <v>-0.0623</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1304000</v>
+        <v>1849400</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.85</v>
+        <v>0.39</v>
       </c>
       <c r="H85" t="n">
-        <v>30.4</v>
+        <v>39.67</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4296,10 +4293,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.419</v>
+        <v>2.942</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.439</v>
+        <v>2.832</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4312,39 +4309,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.07</v>
+        <v>3.03</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.123</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1289800</v>
+        <v>1832600</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="H86" t="n">
-        <v>56.94</v>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.52</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.026</v>
+        <v>3.003</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.868</v>
+        <v>2.813</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4357,39 +4354,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>-0.0204</v>
+        <v>0.21</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.1351</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1275800</v>
+        <v>1796200</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.43</v>
+        <v>1.64</v>
       </c>
       <c r="H87" t="n">
-        <v>52.45</v>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
+        <v>68.78</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>3.862</v>
+        <v>0.185</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>3.589</v>
+        <v>0.183</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4402,39 +4399,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.28</v>
+        <v>0.805</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>-0.0345</v>
+        <v>-0.0062</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1265100</v>
+        <v>1763000</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H88" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.25</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.301</v>
+        <v>0.787</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.298</v>
+        <v>0.765</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4447,39 +4444,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.63</v>
+        <v>0.755</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.137</v>
+        <v>-0.0503</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1258300</v>
+        <v>1738200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H89" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.26</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.532</v>
+        <v>0.737</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.448</v>
+        <v>0.656</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4492,39 +4489,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>-0.0435</v>
+        <v>-0.0373</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1252300</v>
+        <v>1729000</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="H90" t="n">
-        <v>70.23</v>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.344</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.626</v>
+        <v>1.245</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4537,39 +4534,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.265</v>
+        <v>0.75</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.0536</v>
+        <v>-0.0323</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1251100</v>
+        <v>1697200</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.17</v>
+        <v>0.88</v>
       </c>
       <c r="H91" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.1</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.287</v>
+        <v>0.716</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.306</v>
+        <v>0.694</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4582,28 +4579,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.615</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>-0.0315</v>
+        <v>-0.0486</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1247900</v>
+        <v>1695200</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.48</v>
+        <v>0.27</v>
       </c>
       <c r="H92" t="n">
-        <v>41.62</v>
+        <v>27.38</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4611,10 +4608,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.636</v>
+        <v>0.75</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.612</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4627,28 +4624,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E93" s="9" t="n">
-        <v>0.006999999999999999</v>
+        <v>10.02</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1228000</v>
+        <v>1680800</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H93" t="n">
-        <v>46.4</v>
+        <v>47.36</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4656,10 +4653,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>4.367</v>
+        <v>10.022</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>4.458</v>
+        <v>10.203</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4672,39 +4669,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.785</v>
+        <v>0.62</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-0.0309</v>
+        <v>-0.0159</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1182200</v>
+        <v>1653800</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="H94" t="n">
-        <v>54.63</v>
-      </c>
-      <c r="I94" s="8" t="inlineStr">
+        <v>54.39</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.77</v>
+        <v>0.613</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.715</v>
+        <v>0.612</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4717,39 +4714,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1.05</v>
+        <v>3.87</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0541</v>
+        <v>-0.0153</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1160000</v>
+        <v>1628700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
       <c r="H95" t="n">
-        <v>54.03</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.57</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.056</v>
+        <v>3.864</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.901</v>
+        <v>3.59</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4762,28 +4759,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1151000</v>
+        <v>1612800</v>
       </c>
       <c r="G96" s="5" t="n">
         <v>0.39</v>
       </c>
       <c r="H96" t="n">
-        <v>64.43000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4791,10 +4788,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.613</v>
+        <v>1.156</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.599</v>
+        <v>1.073</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4807,39 +4804,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>-0.0373</v>
+        <v>0.62</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1127800</v>
+        <v>1601100</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H97" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.771</v>
+        <v>0.613</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.762</v>
+        <v>0.599</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4852,28 +4849,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.77</v>
+        <v>2.06</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>-0.0314</v>
+        <v>-0.08439999999999999</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1108300</v>
+        <v>1593400</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="H98" t="n">
-        <v>59.05</v>
+        <v>49.55</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4881,10 +4878,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.739</v>
+        <v>2.109</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.656</v>
+        <v>1.966</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4897,28 +4894,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.0299</v>
+        <v>-0.0541</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1077000</v>
+        <v>1590100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H99" t="n">
-        <v>46.17</v>
+        <v>54.03</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4926,10 +4923,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.345</v>
+        <v>1.056</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.245</v>
+        <v>0.901</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4942,28 +4939,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E100" s="9" t="n">
-        <v>0.0214</v>
+        <v>0.27</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1069600</v>
+        <v>1572500</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H100" t="n">
-        <v>47.36</v>
+        <v>31.04</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4971,10 +4968,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>10.022</v>
+        <v>0.288</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>10.203</v>
+        <v>0.306</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4987,28 +4984,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>-0.0421</v>
+        <v>4.3</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1059700</v>
+        <v>1511700</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H101" t="n">
-        <v>48.6</v>
+        <v>45.98</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5016,10 +5013,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.46</v>
+        <v>4.366</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.461</v>
+        <v>4.458</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5032,39 +5029,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.0566</v>
+        <v>-0.0186</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1054700</v>
+        <v>1501100</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="H102" t="n">
-        <v>54.23</v>
-      </c>
-      <c r="I102" s="8" t="inlineStr">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.492</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.48</v>
+        <v>0.626</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5077,40 +5074,36 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.805</v>
+        <v>0.455</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.0319</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1052100</v>
+        <v>1482900</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="H103" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0.765</v>
-      </c>
+        <v>33.62</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
     </row>
@@ -5122,28 +5115,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.585</v>
+        <v>0.37</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>-0.025</v>
+        <v>-0.0133</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1048500</v>
+        <v>1474000</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="H104" t="n">
-        <v>35.84</v>
+        <v>52.46</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5151,10 +5144,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.614</v>
+        <v>0.368</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.634</v>
+        <v>0.368</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5167,39 +5160,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>-0.0127</v>
+        <v>0.34</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1038300</v>
+        <v>1467100</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.31</v>
+        <v>3.11</v>
       </c>
       <c r="H105" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I105" s="8" t="inlineStr">
+        <v>69.77</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>10.294</v>
+        <v>0.314</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>9.558999999999999</v>
+        <v>0.316</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5212,40 +5205,36 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0545</v>
+        <v>-0.0571</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1032400</v>
+        <v>1464100</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H106" t="n">
-        <v>61.87</v>
-      </c>
-      <c r="I106" s="8" t="inlineStr">
+        <v>60.72</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>0.454</v>
-      </c>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
     </row>
@@ -5257,39 +5246,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="E107" s="9" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1031500</v>
+        <v>1448400</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="H107" t="n">
-        <v>27.81</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.83</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>7.573</v>
+        <v>0.25</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>8.07</v>
+        <v>0.254</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5302,33 +5291,40 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.215</v>
+        <v>0.78</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>-0.0444</v>
+        <v>-0.0311</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1004500</v>
+        <v>1443400</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="n"/>
-      <c r="K108" s="2" t="n"/>
+        <v>0.71</v>
+      </c>
+      <c r="H108" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0.762</v>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
     </row>
@@ -5340,39 +5336,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.695</v>
+        <v>0.83</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.0608</v>
+        <v>-0.08289999999999999</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>997200</v>
+        <v>1435000</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="H109" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.03</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.755</v>
+        <v>0.826</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.747</v>
+        <v>0.762</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5385,39 +5381,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1.29</v>
+        <v>2.46</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.012</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>976400</v>
+        <v>1405300</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="H110" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.61</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.226</v>
+        <v>2.462</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1.155</v>
+        <v>2.352</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5430,39 +5426,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>3.05</v>
+        <v>0.615</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>-0.0557</v>
+        <v>-0.0315</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>941800</v>
+        <v>1401800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="H111" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="I111" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.62</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>3.182</v>
+        <v>0.636</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>3.379</v>
+        <v>0.612</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5475,39 +5471,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.26</v>
+        <v>0.385</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0803</v>
+        <v>-0.0723</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>925400</v>
+        <v>1393500</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="H112" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="I112" s="8" t="inlineStr">
+        <v>50.53</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.292</v>
+        <v>0.386</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1.201</v>
+        <v>0.375</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5520,39 +5516,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.835</v>
+        <v>10.8</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>-0.07730000000000001</v>
+        <v>-0.0182</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>908100</v>
+        <v>1375400</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="H113" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I113" s="8" t="inlineStr">
+        <v>66.92</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.827</v>
+        <v>10.288</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.762</v>
+        <v>9.558</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5565,39 +5561,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>0.0231</v>
+        <v>1.09</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>-0.1066</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>900700</v>
+        <v>1374700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H114" t="n">
-        <v>62.64</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.84</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.625</v>
+        <v>1.028</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.533</v>
+        <v>0.869</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5610,39 +5606,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.875</v>
+        <v>1.27</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>-0.0278</v>
+        <v>-0.073</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>879700</v>
+        <v>1366000</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H115" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.85</v>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.95</v>
+        <v>1.293</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.99</v>
+        <v>1.201</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5655,39 +5651,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E116" s="9" t="n">
-        <v>0.03240000000000001</v>
+        <v>2.14</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>876500</v>
+        <v>1344400</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H116" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.18</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>2.191</v>
+        <v>2.105</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2.133</v>
+        <v>2.085</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5700,28 +5696,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>3.27</v>
+        <v>0.4</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.0239</v>
+        <v>-0.0123</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>871400</v>
+        <v>1337700</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="H117" t="n">
-        <v>32</v>
+        <v>32.46</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5729,10 +5725,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>3.449</v>
+        <v>0.42</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>3.644</v>
+        <v>0.439</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5745,39 +5741,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>8.5</v>
+        <v>1.28</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0151</v>
+        <v>-0.0791</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>858800</v>
+        <v>1325300</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="H118" t="n">
-        <v>44.97</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.85</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>8.712999999999999</v>
+        <v>1.225</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>8.68</v>
+        <v>1.155</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5790,28 +5786,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.14</v>
+        <v>0.425</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-0.1024</v>
+        <v>-0.0761</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>842800</v>
+        <v>1279900</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="H119" t="n">
-        <v>57.46</v>
+        <v>55.26</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5819,10 +5815,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.09</v>
+        <v>0.418</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.84</v>
+        <v>0.371</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5835,39 +5831,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2.94</v>
+        <v>0.28</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>-0.0034</v>
+        <v>-0.0345</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>817900</v>
+        <v>1265100</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H120" t="n">
-        <v>77.43000000000001</v>
-      </c>
-      <c r="I120" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.9</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>2.675</v>
+        <v>0.301</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2.31</v>
+        <v>0.298</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5880,28 +5876,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>-0.07629999999999999</v>
+        <v>0.215</v>
+      </c>
+      <c r="E121" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>810500</v>
+        <v>1257200</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.42</v>
+        <v>0.06</v>
       </c>
       <c r="H121" t="n">
-        <v>43.47</v>
+        <v>39.32</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5909,10 +5905,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.268</v>
+        <v>0.224</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1.316</v>
+        <v>0.241</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5925,28 +5921,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2.46</v>
+        <v>0.705</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>-0.012</v>
+        <v>-0.0473</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>780700</v>
+        <v>1219200</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="H122" t="n">
-        <v>52.61</v>
+        <v>40.1</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5954,10 +5950,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>2.462</v>
+        <v>0.755</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.352</v>
+        <v>0.747</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5970,39 +5966,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>-0.0183</v>
+        <v>-0.0545</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>766000</v>
+        <v>1187000</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="H123" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.87</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.579</v>
+        <v>0.481</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.62</v>
+        <v>0.454</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6015,39 +6011,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>7.72</v>
+        <v>0.5</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-0.0302</v>
+        <v>-0.0566</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>717100</v>
+        <v>1184700</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="H124" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="I124" s="8" t="inlineStr">
+        <v>54.23</v>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>7.289</v>
+        <v>0.492</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>6.785</v>
+        <v>0.48</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6060,39 +6056,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1.18</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-0.0484</v>
+        <v>-0.0104</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>700000</v>
+        <v>1147200</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="H125" t="n">
-        <v>52.57</v>
-      </c>
-      <c r="I125" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.87</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.161</v>
+        <v>8.715999999999999</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1.169</v>
+        <v>8.680999999999999</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6105,28 +6101,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.505</v>
+        <v>0.585</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.0288</v>
+        <v>-0.025</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>648900</v>
+        <v>1145300</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="H126" t="n">
-        <v>41.98</v>
+        <v>35.84</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6134,10 +6130,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.523</v>
+        <v>0.614</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.533</v>
+        <v>0.634</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6150,39 +6146,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1.01</v>
+        <v>0.665</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>0</v>
+        <v>0.0231</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>648800</v>
+        <v>1124000</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="H127" t="n">
-        <v>57.41</v>
-      </c>
-      <c r="I127" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.64</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.999</v>
+        <v>0.625</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.981</v>
+        <v>0.533</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6195,39 +6191,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.04</v>
+        <v>3.06</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>-0.028</v>
+        <v>-0.0526</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>646900</v>
+        <v>1079200</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="H128" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="I128" s="8" t="inlineStr">
+        <v>37.92</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.058</v>
+        <v>3.183</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.19</v>
+        <v>3.379</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6240,28 +6236,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.585</v>
+        <v>0.88</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>-0.0565</v>
+        <v>-0.0222</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>646400</v>
+        <v>1070700</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="H129" t="n">
-        <v>43.84</v>
+        <v>22.3</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6269,10 +6265,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.612</v>
+        <v>0.95</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.607</v>
+        <v>0.99</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6285,40 +6281,33 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="E130" s="9" t="n">
-        <v>0.0279</v>
+        <v>0.215</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>621700</v>
+        <v>1053900</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H130" t="n">
-        <v>36.34</v>
+        <v>0.06</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J130" s="2" t="n">
-        <v>6.454</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>6.82</v>
-      </c>
+      <c r="J130" s="2" t="n"/>
+      <c r="K130" s="2" t="n"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
     </row>
@@ -6330,28 +6319,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.9</v>
+        <v>3.27</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>-0.0217</v>
+        <v>-0.0239</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>614000</v>
+        <v>1048700</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H131" t="n">
-        <v>50.4</v>
+        <v>32</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6359,10 +6348,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.907</v>
+        <v>3.449</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.864</v>
+        <v>3.644</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6375,39 +6364,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>5</v>
+        <v>7.69</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.0177</v>
+        <v>-0.0339</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>539900</v>
+        <v>1008900</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="H132" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.51</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>5.045</v>
+        <v>7.287</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>5.058</v>
+        <v>6.785</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6420,39 +6409,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.12</v>
+        <v>0.225</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>539000</v>
+        <v>1006700</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
       <c r="H133" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="I133" s="8" t="inlineStr">
+        <v>61.87</v>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.103</v>
+        <v>0.209</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.085</v>
+        <v>0.173</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6465,28 +6454,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>-0.0694</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>528400</v>
+        <v>993200</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="H134" t="n">
-        <v>45.33</v>
+        <v>58.22</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6494,10 +6483,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.658</v>
+        <v>1.091</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>1.676</v>
+        <v>0.84</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6510,39 +6499,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>-0.0262</v>
+        <v>2.22</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>525700</v>
+        <v>973900</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="H135" t="n">
-        <v>65.39</v>
-      </c>
-      <c r="I135" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.16</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>2.72</v>
+        <v>2.19</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2.072</v>
+        <v>2.133</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6555,39 +6544,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>-0.0413</v>
+        <v>12.92</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>510400</v>
+        <v>973000</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="H136" t="n">
-        <v>43.88</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.83</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>4.327</v>
+        <v>13.018</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>4.358</v>
+        <v>13.543</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6600,28 +6589,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>-0.0424</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>509900</v>
+        <v>968900</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="H137" t="n">
-        <v>40.51</v>
+        <v>42.7</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6629,16 +6618,1501 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.683</v>
+        <v>1.267</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1.652</v>
+        <v>1.316</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>952100</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H138" t="n">
+        <v>52.57</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>-0.04480000000000001</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>860000</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H139" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-0.0565</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>848100</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H140" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>816000</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H141" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>6.453</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>815400</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H142" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>2.072</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>766000</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>743100</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H144" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>4.321</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>4.357</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>-0.0288</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>725200</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H145" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>723100</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H146" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>2.592</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>721700</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H147" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>-0.0352</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>707400</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H148" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>701800</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H149" t="n">
+        <v>43.22</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H150" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>665900</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H151" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>-0.06759999999999999</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>657300</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H152" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>2.187</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>654100</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H153" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>5.048</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>5.058</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>649300</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H154" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>630100</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H155" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>-0.0364</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>624200</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H156" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>1.684</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>-0.06570000000000001</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>608400</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H157" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>-0.0636</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>604600</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H158" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>570000</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H159" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>-0.0272</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>559400</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H160" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>-0.0383</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>549500</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H161" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>2.054</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>2.082</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>-0.004500000000000001</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>539700</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>4.803</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>-0.0538</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>536800</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H163" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>1.732</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>-0.0249</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>536700</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H164" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>6.137</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>6.387</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>534800</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H165" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>2.221</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>533300</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H166" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>-0.06150000000000001</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>529800</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H167" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>519800</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H168" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>-0.0541</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>510000</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H169" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>509900</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H170" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M137"/>
+  <autoFilter ref="A1:M170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
+++ b/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-13" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.1389</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>64542300</v>
+        <v>65644000</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>48.11</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.1765</v>
+        <v>-0.1176</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>56442400</v>
+        <v>58782800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H3" t="n">
-        <v>22.22</v>
+        <v>22.65</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.385</v>
@@ -648,10 +648,10 @@
         <v>-0.07690000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>36169100</v>
+        <v>37602000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="H4" t="n">
         <v>48.22</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>29413500</v>
+        <v>30579800</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H5" t="n">
         <v>63.56</v>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>24379200</v>
+        <v>29009900</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.66</v>
+        <v>0.48</v>
       </c>
       <c r="H6" t="n">
-        <v>70.36</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.361</v>
+        <v>0.284</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.243</v>
+        <v>0.247</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,28 +768,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-0.058</v>
+        <v>0.395</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>22004700</v>
+        <v>28707300</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="H7" t="n">
-        <v>68.2</v>
+        <v>71.42</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.283</v>
+        <v>0.361</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.246</v>
+        <v>0.243</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -828,10 +828,10 @@
         <v>-0.1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20479300</v>
+        <v>20763600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="H8" t="n">
         <v>43.31</v>
@@ -873,10 +873,10 @@
         <v>0.0142</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16209800</v>
+        <v>18559600</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
         <v>76.59999999999999</v>
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.575</v>
+        <v>0.585</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.0873</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13402700</v>
+        <v>15049800</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="H10" t="n">
-        <v>51.64</v>
+        <v>53.37</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.58</v>
+        <v>0.581</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.522</v>
+        <v>0.523</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.1183</v>
+        <v>-0.129</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13154500</v>
+        <v>13254600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="H11" t="n">
-        <v>61.28</v>
+        <v>60.08</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11550800</v>
+        <v>11556600</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.33</v>
@@ -1031,28 +1031,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.5</v>
+        <v>0.105</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.2021</v>
+        <v>-0.0455</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9288600</v>
+        <v>11208100</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="H13" t="n">
-        <v>21.07</v>
+        <v>37.13</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.861</v>
+        <v>0.114</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2.013</v>
+        <v>0.122</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,39 +1076,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.105</v>
+        <v>2.7</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.0455</v>
+        <v>-0.0253</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9182100</v>
+        <v>11178100</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.39</v>
+        <v>0.63</v>
       </c>
       <c r="H14" t="n">
-        <v>37.13</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.58</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.114</v>
+        <v>2.633</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.122</v>
+        <v>2.508</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
+        <v>1.48</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.2128</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8878800</v>
+        <v>11133400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>11.55</v>
+        <v>2.88</v>
       </c>
       <c r="H15" t="n">
-        <v>54.59</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.51</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.186</v>
+        <v>1.859</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.188</v>
+        <v>2.013</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1181,10 +1181,10 @@
         <v>-0.008</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8817600</v>
+        <v>11064700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H16" t="n">
         <v>68.95999999999999</v>
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.2</v>
+        <v>0.2667</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8692500</v>
+        <v>9974000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2.91</v>
+        <v>3.33</v>
       </c>
       <c r="H17" t="n">
-        <v>55.2</v>
+        <v>59.78</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0.092</v>
@@ -1256,39 +1256,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-0.0345</v>
+        <v>0.19</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>8396900</v>
+        <v>9047900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.32</v>
+        <v>11.77</v>
       </c>
       <c r="H18" t="n">
-        <v>42.91</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.59</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.154</v>
+        <v>0.186</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.148</v>
+        <v>0.188</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,39 +1301,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.74</v>
+        <v>0.14</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-0.0108</v>
+        <v>-0.0345</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8351800</v>
+        <v>8856900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
       <c r="H19" t="n">
-        <v>61.19</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.91</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.636</v>
+        <v>0.154</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2.509</v>
+        <v>0.148</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,28 +1346,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.355</v>
+        <v>0.865</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.0139</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8095800</v>
+        <v>8334300</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H20" t="n">
-        <v>57.67</v>
+        <v>46.92</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.345</v>
+        <v>0.868</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.326</v>
+        <v>0.869</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1391,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.425</v>
+        <v>0.355</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.023</v>
+        <v>-0.0139</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6896800</v>
+        <v>8186300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.29</v>
+        <v>1.09</v>
       </c>
       <c r="H21" t="n">
-        <v>57.56</v>
+        <v>57.67</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.411</v>
+        <v>0.345</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.35</v>
+        <v>0.326</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.08779999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6881900</v>
+        <v>7997700</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.68</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1481,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>NOVAMSC</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.865</v>
+        <v>0.05</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6755700</v>
+        <v>7973700</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.36</v>
+        <v>16.56</v>
       </c>
       <c r="H23" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.58</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.868</v>
+        <v>0.057</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.869</v>
+        <v>0.062</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,39 +1526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.445</v>
+        <v>4.92</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0334</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6750100</v>
+        <v>7807100</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="H24" t="n">
-        <v>23.73</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.4</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.539</v>
+        <v>4.925</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.737</v>
+        <v>4.667</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.39</v>
+        <v>0.455</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.0127</v>
+        <v>-0.0421</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6411700</v>
+        <v>7651000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="H25" t="n">
-        <v>33.82</v>
+        <v>24.62</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.401</v>
+        <v>0.54</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.409</v>
+        <v>0.737</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,28 +1616,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-0.0354</v>
+        <v>0.775</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6185400</v>
+        <v>7278600</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.25</v>
+        <v>0.49</v>
       </c>
       <c r="H26" t="n">
-        <v>51.93</v>
+        <v>50.45</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.924</v>
+        <v>0.774</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4.667</v>
+        <v>0.775</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,28 +1661,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6057100</v>
+        <v>7115300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H27" t="n">
-        <v>58.27</v>
+        <v>57.56</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.411</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,39 +1706,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.67</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-0.0946</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5785600</v>
+        <v>7074000</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.39</v>
+        <v>0.84</v>
       </c>
       <c r="H28" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.83</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.774</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.775</v>
+        <v>0.68</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1751,28 +1751,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0026</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NOVAMSC</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0286</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5652300</v>
+        <v>6940900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>11.74</v>
+        <v>1.58</v>
       </c>
       <c r="H29" t="n">
-        <v>36.58</v>
+        <v>37.38</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.057</v>
+        <v>0.176</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.062</v>
+        <v>0.185</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,39 +1796,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.39</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5612200</v>
+        <v>6413300</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>3.47</v>
+        <v>0.58</v>
       </c>
       <c r="H30" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.82</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.238</v>
+        <v>0.401</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.243</v>
+        <v>0.409</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1841,39 +1841,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>-0.0741</v>
+        <v>0.315</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5493200</v>
+        <v>6352200</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.95</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.52</v>
+        <v>0.307</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.53</v>
+        <v>0.296</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1886,28 +1886,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.045</v>
+        <v>0.315</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.125</v>
+        <v>0.05</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5430500</v>
+        <v>6258700</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>2.83</v>
+        <v>1.05</v>
       </c>
       <c r="H32" t="n">
-        <v>54.63</v>
+        <v>73.67</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.042</v>
+        <v>0.292</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.047</v>
+        <v>0.276</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1931,39 +1931,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-0.0741</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5229200</v>
+        <v>5959200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="H33" t="n">
-        <v>73.67</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.62</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.292</v>
+        <v>0.52</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.276</v>
+        <v>0.53</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1976,39 +1976,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-0.1468</v>
+        <v>0.245</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4990700</v>
+        <v>5832300</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.9</v>
+        <v>3.61</v>
       </c>
       <c r="H34" t="n">
-        <v>21.66</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.56</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.58</v>
+        <v>0.237</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.637</v>
+        <v>0.243</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2021,39 +2021,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.08960000000000001</v>
+        <v>0.045</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.125</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4981900</v>
+        <v>5530500</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.84</v>
+        <v>2.88</v>
       </c>
       <c r="H35" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.63</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.324</v>
+        <v>0.042</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.338</v>
+        <v>0.047</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2066,28 +2066,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0117</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SMRT</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.155</v>
+        <v>0.28</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.1389</v>
+        <v>-0.0667</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4638700</v>
+        <v>5439900</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1.41</v>
+        <v>0.44</v>
       </c>
       <c r="H36" t="n">
-        <v>26.85</v>
+        <v>47.07</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.183</v>
+        <v>0.291</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.193</v>
+        <v>0.281</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2111,28 +2111,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.05</v>
+        <v>0.465</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.0187</v>
+        <v>-0.1468</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4613100</v>
+        <v>5332100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.37</v>
+        <v>0.96</v>
       </c>
       <c r="H37" t="n">
-        <v>47.22</v>
+        <v>21.66</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.07</v>
+        <v>0.58</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.038</v>
+        <v>0.637</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         <v>0.0193</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4426700</v>
+        <v>5189300</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H38" t="n">
         <v>39.27</v>
@@ -2201,28 +2201,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2.77</v>
+        <v>1.68</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-0.0281</v>
+        <v>-0.0562</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4392800</v>
+        <v>5125600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.31</v>
+        <v>1.03</v>
       </c>
       <c r="H39" t="n">
-        <v>49.79</v>
+        <v>40.63</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.793</v>
+        <v>1.747</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2.702</v>
+        <v>1.776</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2246,28 +2246,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.275</v>
+        <v>1.03</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-0.0833</v>
+        <v>-0.0374</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4135900</v>
+        <v>5070500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="H40" t="n">
-        <v>45.58</v>
+        <v>44.35</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.29</v>
+        <v>1.068</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.281</v>
+        <v>1.038</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2291,28 +2291,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.29</v>
+        <v>0.305</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.0584</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4016900</v>
+        <v>5032700</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.32</v>
+        <v>0.85</v>
       </c>
       <c r="H41" t="n">
-        <v>60.73</v>
+        <v>40.78</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.242</v>
+        <v>0.324</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.018</v>
+        <v>0.338</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2336,28 +2336,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.9</v>
+        <v>1.28</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-0.0674</v>
+        <v>-0.1409</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3988100</v>
+        <v>4975600</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.5</v>
+        <v>2.82</v>
       </c>
       <c r="H42" t="n">
-        <v>45.8</v>
+        <v>20.62</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.955</v>
+        <v>1.487</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.826</v>
+        <v>1.611</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2381,28 +2381,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0117</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SMRT</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.69</v>
+        <v>0.155</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.0506</v>
+        <v>-0.1389</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3948000</v>
+        <v>4754500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.79</v>
+        <v>1.45</v>
       </c>
       <c r="H43" t="n">
-        <v>41.62</v>
+        <v>26.85</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.748</v>
+        <v>0.183</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.777</v>
+        <v>0.193</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2426,28 +2426,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.655</v>
+        <v>1.3</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3937000</v>
+        <v>4744600</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.43</v>
+        <v>1.56</v>
       </c>
       <c r="H44" t="n">
-        <v>49.61</v>
+        <v>61.96</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.67</v>
+        <v>1.243</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.61</v>
+        <v>1.018</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2471,28 +2471,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0.0095</v>
+        <v>2.76</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3928500</v>
+        <v>4730400</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="H45" t="n">
-        <v>56.81</v>
+        <v>49.06</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.513</v>
+        <v>2.792</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.44</v>
+        <v>2.701</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2525,19 +2525,19 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>-0.0444</v>
+        <v>0.225</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3674800</v>
+        <v>4706300</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="H46" t="n">
-        <v>30.21</v>
+        <v>33.08</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.246</v>
+        <v>0.247</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0.301</v>
@@ -2561,39 +2561,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.28</v>
+        <v>0.895</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>-0.0508</v>
+        <v>-0.0725</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3641700</v>
+        <v>4331900</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H47" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.2</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.278</v>
+        <v>0.955</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.302</v>
+        <v>0.825</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2606,28 +2606,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-0.0333</v>
+        <v>0.535</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.019</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3574100</v>
+        <v>4331400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H48" t="n">
-        <v>27.94</v>
+        <v>57.67</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.163</v>
+        <v>0.514</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.199</v>
+        <v>0.44</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2651,28 +2651,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.28</v>
+        <v>0.14</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-0.1409</v>
+        <v>-0.0667</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3554900</v>
+        <v>4296500</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2.02</v>
+        <v>0.25</v>
       </c>
       <c r="H49" t="n">
-        <v>20.62</v>
+        <v>25.99</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.487</v>
+        <v>0.163</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.611</v>
+        <v>0.199</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2696,28 +2696,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2.07</v>
+        <v>0.655</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-0.0417</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3535000</v>
+        <v>4236600</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="H50" t="n">
-        <v>36.93</v>
+        <v>49.61</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.212</v>
+        <v>0.67</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.216</v>
+        <v>0.61</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2741,28 +2741,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.425</v>
+        <v>5.41</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-0.0761</v>
+        <v>-0.0509</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3294300</v>
+        <v>4041800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.91</v>
+        <v>0.3</v>
       </c>
       <c r="H51" t="n">
-        <v>41.9</v>
+        <v>43.85</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.455</v>
+        <v>5.623</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.422</v>
+        <v>5.334</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2786,33 +2786,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.1</v>
+        <v>0.83</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0119</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3274100</v>
+        <v>4035100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.21</v>
+        <v>5.68</v>
+      </c>
+      <c r="H52" t="n">
+        <v>32.27</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
+      <c r="J52" s="2" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.864</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
     </row>
@@ -2824,28 +2831,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.43</v>
+        <v>0.275</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0678</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3203500</v>
+        <v>3987200</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="H53" t="n">
-        <v>46.39</v>
+        <v>47.72</v>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
@@ -2853,10 +2860,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.449</v>
+        <v>0.278</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.428</v>
+        <v>0.302</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2869,39 +2876,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0</v>
+        <v>0.475</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3173200</v>
+        <v>3986400</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.17</v>
+        <v>0.54</v>
       </c>
       <c r="H54" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.32</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.307</v>
+        <v>0.52</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.296</v>
+        <v>0.569</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2914,39 +2921,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>6.62</v>
+        <v>2.08</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.0236</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3070600</v>
+        <v>3882000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.62</v>
+        <v>0.26</v>
       </c>
       <c r="H55" t="n">
-        <v>62.92</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.55</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.914</v>
+        <v>2.213</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>5.804</v>
+        <v>2.217</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2959,28 +2966,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0027</v>
+        <v>1.18</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3019300</v>
+        <v>3783400</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="H56" t="n">
-        <v>55.54</v>
+        <v>27.69</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2988,10 +2995,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.603</v>
+        <v>1.275</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.784</v>
+        <v>1.378</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3004,39 +3011,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.48</v>
+        <v>0.15</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.0323</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2966300</v>
+        <v>3713900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.4</v>
+        <v>1.87</v>
       </c>
       <c r="H57" t="n">
-        <v>29.38</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.58</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.52</v>
+        <v>0.153</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.569</v>
+        <v>0.152</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3049,39 +3056,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>5.36</v>
+        <v>6.5</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>-0.0596</v>
+        <v>-0.0413</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2917000</v>
+        <v>3526800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.21</v>
+        <v>0.72</v>
       </c>
       <c r="H58" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.63</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5.618</v>
+        <v>5.902</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>5.333</v>
+        <v>5.801</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3094,39 +3101,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2878300</v>
+        <v>3479400</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
       <c r="H59" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.295</v>
+        <v>0.613</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.296</v>
+        <v>0.612</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3139,39 +3146,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.8</v>
+        <v>0.415</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2870000</v>
+        <v>3449900</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>63.71</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.81</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.755</v>
+        <v>0.425</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.668</v>
+        <v>0.413</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3184,39 +3191,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.415</v>
+        <v>0.43</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2825100</v>
+        <v>3395300</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>48.81</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.24</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.425</v>
+        <v>0.456</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.413</v>
+        <v>0.422</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3229,28 +3236,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>-0.0495</v>
+        <v>7.27</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2722300</v>
+        <v>3369900</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H62" t="n">
-        <v>55.83</v>
+        <v>28.52</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3258,10 +3265,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>3.971</v>
+        <v>7.573</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3.463</v>
+        <v>8.07</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3274,40 +3281,33 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>5.49</v>
+        <v>0.105</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0455</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2705700</v>
+        <v>3326700</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="H63" t="n">
-        <v>51.47</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>5.479</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>5.366</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
     </row>
@@ -3319,39 +3319,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>4.69</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2701100</v>
+        <v>3310800</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
       <c r="H64" t="n">
-        <v>49.02</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.19</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.626</v>
+        <v>4.719</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.585</v>
+        <v>4.884</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3364,39 +3364,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.765</v>
+        <v>0.435</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0438</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2557700</v>
+        <v>3264300</v>
       </c>
       <c r="G65" s="5" t="n">
         <v>0.31</v>
       </c>
       <c r="H65" t="n">
-        <v>46.94</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.43</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.778</v>
+        <v>0.45</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.773</v>
+        <v>0.428</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3409,39 +3409,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.385</v>
+        <v>2.62</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.04940000000000001</v>
+        <v>-0.0296</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2546400</v>
+        <v>3263000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1.24</v>
+        <v>0.53</v>
       </c>
       <c r="H66" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.48</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.386</v>
+        <v>2.628</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.391</v>
+        <v>2.586</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3454,39 +3454,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.605</v>
+        <v>4.04</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2545300</v>
+        <v>3254100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.65</v>
+        <v>0.38</v>
       </c>
       <c r="H67" t="n">
-        <v>53.12</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.597</v>
+        <v>3.972</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.583</v>
+        <v>3.464</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3499,28 +3499,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>0</v>
+        <v>3.65</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2489800</v>
+        <v>3227000</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H68" t="n">
-        <v>49.32</v>
+        <v>55.05</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.162</v>
+        <v>3.601</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.122</v>
+        <v>2.784</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3544,28 +3544,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.315</v>
+        <v>0.795</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0479</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2430500</v>
+        <v>3084400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="H69" t="n">
-        <v>26.33</v>
+        <v>62.51</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.358</v>
+        <v>0.755</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.382</v>
+        <v>0.668</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3589,28 +3589,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2.79</v>
+        <v>5.49</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>-0.0245</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2419500</v>
+        <v>3035200</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.26</v>
+        <v>0.86</v>
       </c>
       <c r="H70" t="n">
-        <v>53.07</v>
+        <v>51.47</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.779</v>
+        <v>5.479</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2.611</v>
+        <v>5.366</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.0123</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2396000</v>
+        <v>3023700</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="H71" t="n">
-        <v>37.52</v>
+        <v>36.45</v>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.664</v>
+        <v>1.663</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>1.779</v>
@@ -3679,28 +3679,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.0263</v>
+        <v>2.78</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2368600</v>
+        <v>2932800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="H72" t="n">
-        <v>44.19</v>
+        <v>52.47</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>4.719</v>
+        <v>2.778</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.884</v>
+        <v>2.61</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3724,39 +3724,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.07440000000000001</v>
+        <v>1.15</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2341400</v>
+        <v>2932400</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="H73" t="n">
-        <v>55.52</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.32</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.551</v>
+        <v>1.162</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.497</v>
+        <v>1.122</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3769,28 +3769,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2297400</v>
+        <v>2878300</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.23</v>
+        <v>0.99</v>
       </c>
       <c r="H74" t="n">
-        <v>43.38</v>
+        <v>49.15</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.319</v>
+        <v>0.295</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.308</v>
+        <v>0.296</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3814,39 +3814,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2.77</v>
+        <v>0.6</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>-0.061</v>
+        <v>-0.0698</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2294900</v>
+        <v>2738700</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H75" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.99</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.956</v>
+        <v>0.597</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>3.03</v>
+        <v>0.582</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3859,39 +3859,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.08</v>
+        <v>0.765</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.0438</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2153200</v>
+        <v>2705500</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H76" t="n">
-        <v>55.63</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.94</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.072</v>
+        <v>0.778</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.925</v>
+        <v>0.773</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3904,39 +3904,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>-0.0693</v>
+        <v>-0.0167</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2149600</v>
+        <v>2671600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.63</v>
+        <v>1.11</v>
       </c>
       <c r="H77" t="n">
-        <v>76.73999999999999</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.34</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.493</v>
+        <v>0.634</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3949,28 +3949,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.18</v>
+        <v>0.315</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2140500</v>
+        <v>2643300</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="H78" t="n">
-        <v>27.69</v>
+        <v>26.33</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.275</v>
+        <v>0.358</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.378</v>
+        <v>0.382</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3994,28 +3994,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.355</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.0779</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2126600</v>
+        <v>2615500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="H79" t="n">
-        <v>29.22</v>
+        <v>53.3</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7.574</v>
+        <v>0.354</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>8.071</v>
+        <v>0.323</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4039,39 +4039,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2118200</v>
+        <v>2589400</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H80" t="n">
-        <v>46.95</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.52</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.46</v>
+        <v>0.551</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.461</v>
+        <v>0.497</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4084,28 +4084,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.78</v>
+        <v>0.385</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2014100</v>
+        <v>2557900</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.15</v>
+        <v>1.25</v>
       </c>
       <c r="H81" t="n">
-        <v>53.81</v>
+        <v>49.26</v>
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.77</v>
+        <v>0.386</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.715</v>
+        <v>0.391</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4129,39 +4129,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.355</v>
+        <v>0.385</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.0779</v>
+        <v>-0.0723</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1930500</v>
+        <v>2555100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H82" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.53</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.354</v>
+        <v>0.386</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.323</v>
+        <v>0.375</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4174,39 +4174,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2.93</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.0068</v>
+        <v>-0.0486</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1885500</v>
+        <v>2551600</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="H83" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.38</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.674</v>
+        <v>0.75</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2.309</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4219,39 +4219,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.635</v>
+        <v>1.26</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>-0.1301</v>
+        <v>-0.0233</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1877800</v>
+        <v>2518500</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="H84" t="n">
-        <v>66.91</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.86</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.532</v>
+        <v>1.317</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.448</v>
+        <v>1.307</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4264,28 +4264,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>2.71</v>
+        <v>0.455</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.0623</v>
+        <v>-0.0421</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1849400</v>
+        <v>2474800</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.39</v>
+        <v>1.32</v>
       </c>
       <c r="H85" t="n">
-        <v>39.67</v>
+        <v>48.6</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.942</v>
+        <v>0.46</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2.832</v>
+        <v>0.461</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4309,28 +4309,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.0576</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1832600</v>
+        <v>2447000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="H86" t="n">
-        <v>53.52</v>
+        <v>35.38</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3.003</v>
+        <v>2.957</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2.813</v>
+        <v>3.031</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4354,28 +4354,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.1351</v>
+        <v>0.785</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0309</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1796200</v>
+        <v>2446600</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1.64</v>
+        <v>0.18</v>
       </c>
       <c r="H87" t="n">
-        <v>68.78</v>
+        <v>54.63</v>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.185</v>
+        <v>0.77</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.183</v>
+        <v>0.715</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4399,28 +4399,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>-0.0062</v>
+        <v>8.050000000000001</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1763000</v>
+        <v>2334100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.29</v>
+        <v>1.45</v>
       </c>
       <c r="H88" t="n">
-        <v>67.25</v>
+        <v>58.68</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.787</v>
+        <v>7.762</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.765</v>
+        <v>7.901</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4444,39 +4444,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.755</v>
+        <v>1.07</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.0503</v>
+        <v>-0.0614</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1738200</v>
+        <v>2328000</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H89" t="n">
-        <v>56.26</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.737</v>
+        <v>1.071</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.656</v>
+        <v>0.925</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4489,28 +4489,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>-0.0373</v>
+        <v>10</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0194</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1729000</v>
+        <v>2294300</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="H90" t="n">
-        <v>45</v>
+        <v>46.16</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.344</v>
+        <v>10.02</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.245</v>
+        <v>10.203</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4534,28 +4534,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.0323</v>
+        <v>-0.0594</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1697200</v>
+        <v>2276200</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="H91" t="n">
-        <v>58.1</v>
+        <v>78.03</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.716</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.694</v>
+        <v>0.493</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4579,39 +4579,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>-0.0486</v>
+        <v>-0.0062</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1695200</v>
+        <v>2225500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="H92" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.25</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.75</v>
+        <v>0.787</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4624,28 +4624,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0.0214</v>
+        <v>0.37</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1680800</v>
+        <v>2164200</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H93" t="n">
-        <v>47.36</v>
+        <v>52.46</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>10.022</v>
+        <v>0.368</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>10.203</v>
+        <v>0.368</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4669,39 +4669,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.62</v>
+        <v>2.72</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0588</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1653800</v>
+        <v>2119800</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="H94" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.02</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.613</v>
+        <v>2.943</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.612</v>
+        <v>2.832</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4714,28 +4714,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>3.87</v>
+        <v>2.93</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0153</v>
+        <v>-0.0068</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1628700</v>
+        <v>2043500</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="H95" t="n">
-        <v>53.57</v>
+        <v>76.3</v>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>3.864</v>
+        <v>2.674</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3.59</v>
+        <v>2.309</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4759,39 +4759,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.025</v>
+        <v>-0.1233</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1612800</v>
+        <v>2017100</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H96" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.156</v>
+        <v>0.533</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1.073</v>
+        <v>0.448</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4804,28 +4804,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.0373</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1601100</v>
+        <v>2008500</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H97" t="n">
-        <v>64.43000000000001</v>
+        <v>45</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.613</v>
+        <v>1.344</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.599</v>
+        <v>1.245</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4849,28 +4849,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.06</v>
+        <v>3.04</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1593400</v>
+        <v>1980000</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H98" t="n">
-        <v>49.55</v>
+        <v>53.95</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.109</v>
+        <v>3.004</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1.966</v>
+        <v>2.813</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4894,39 +4894,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.0541</v>
+        <v>-0.0062</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1590100</v>
+        <v>1960700</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.33</v>
+        <v>0.97</v>
       </c>
       <c r="H99" t="n">
-        <v>54.03</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.26</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.056</v>
+        <v>0.773</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.901</v>
+        <v>0.762</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4939,28 +4939,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.0357</v>
+        <v>4.29</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0023</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1572500</v>
+        <v>1930600</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H100" t="n">
-        <v>31.04</v>
+        <v>45.56</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.288</v>
+        <v>4.365</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.306</v>
+        <v>4.457</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4984,28 +4984,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.215</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1511700</v>
+        <v>1886200</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H101" t="n">
-        <v>45.98</v>
+        <v>39.32</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>4.366</v>
+        <v>0.224</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>4.458</v>
+        <v>0.241</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5029,39 +5029,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0503</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1501100</v>
+        <v>1847700</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="H102" t="n">
-        <v>76.04000000000001</v>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.26</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.737</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.626</v>
+        <v>0.656</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5074,36 +5074,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.455</v>
+        <v>1.17</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0319</v>
+        <v>-0.025</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1482900</v>
+        <v>1819400</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="H103" t="n">
-        <v>33.62</v>
+        <v>56.2</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="n"/>
+      <c r="J103" s="2" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>1.073</v>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
     </row>
@@ -5115,39 +5119,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>-0.0133</v>
+        <v>0.215</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0.1622</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1474000</v>
+        <v>1805500</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.22</v>
+        <v>1.64</v>
       </c>
       <c r="H104" t="n">
-        <v>52.46</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.75</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.368</v>
+        <v>0.186</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.368</v>
+        <v>0.183</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5160,28 +5164,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0.0625</v>
+        <v>3.88</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1467100</v>
+        <v>1802200</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>3.11</v>
+        <v>0.6</v>
       </c>
       <c r="H105" t="n">
-        <v>69.77</v>
+        <v>54.14</v>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
@@ -5189,10 +5193,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.314</v>
+        <v>3.865</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.316</v>
+        <v>3.59</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5205,36 +5209,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.33</v>
+        <v>10.7</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0571</v>
+        <v>-0.0273</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1464100</v>
+        <v>1792300</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="H106" t="n">
-        <v>60.72</v>
+        <v>64.11</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="2" t="n"/>
+      <c r="J106" s="2" t="n">
+        <v>10.278</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>9.555999999999999</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
     </row>
@@ -5246,40 +5254,36 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.25</v>
+        <v>0.455</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0319</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1448400</v>
+        <v>1788400</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="H107" t="n">
-        <v>49.83</v>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>0.254</v>
-      </c>
+        <v>33.62</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
     </row>
@@ -5291,28 +5295,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.78</v>
+        <v>0.745</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>-0.0311</v>
+        <v>-0.0387</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1443400</v>
+        <v>1742000</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="H108" t="n">
-        <v>52.86</v>
+        <v>57.1</v>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
@@ -5320,10 +5324,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.771</v>
+        <v>0.716</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.762</v>
+        <v>0.694</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5336,28 +5340,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.83</v>
+        <v>1.1</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.08289999999999999</v>
+        <v>-0.0984</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1435000</v>
+        <v>1740300</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H109" t="n">
-        <v>53.03</v>
+        <v>59.84</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
@@ -5365,10 +5369,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.826</v>
+        <v>1.029</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.762</v>
+        <v>0.869</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5381,28 +5385,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2.46</v>
+        <v>1.06</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>-0.012</v>
+        <v>-0.045</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1405300</v>
+        <v>1712200</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H110" t="n">
-        <v>52.61</v>
+        <v>55.56</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5410,10 +5414,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.462</v>
+        <v>1.057</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2.352</v>
+        <v>0.901</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5426,39 +5430,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>-0.0315</v>
+        <v>2.13</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1401800</v>
+        <v>1710100</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.54</v>
+        <v>0.09</v>
       </c>
       <c r="H111" t="n">
-        <v>41.62</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.85</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.636</v>
+        <v>2.104</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.612</v>
+        <v>2.085</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5471,39 +5475,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.385</v>
+        <v>2.1</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0723</v>
+        <v>-0.0667</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1393500</v>
+        <v>1701500</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.11</v>
+        <v>0.72</v>
       </c>
       <c r="H112" t="n">
-        <v>50.53</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.61</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.386</v>
+        <v>2.113</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.375</v>
+        <v>1.967</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5516,28 +5520,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>10.8</v>
+        <v>0.83</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.08289999999999999</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1375400</v>
+        <v>1679800</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
       <c r="H113" t="n">
-        <v>66.92</v>
+        <v>53.03</v>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
@@ -5545,10 +5549,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>10.288</v>
+        <v>0.826</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>9.558</v>
+        <v>0.762</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5561,39 +5565,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1.09</v>
+        <v>2.46</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.1066</v>
+        <v>-0.012</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1374700</v>
+        <v>1607400</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="H114" t="n">
-        <v>58.84</v>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.61</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.028</v>
+        <v>2.462</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.869</v>
+        <v>2.352</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5606,39 +5610,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>-0.073</v>
+        <v>0.62</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1366000</v>
+        <v>1601100</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="H115" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.293</v>
+        <v>0.613</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1.201</v>
+        <v>0.599</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5651,39 +5655,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.27</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1344400</v>
+        <v>1595600</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H116" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.04</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>2.105</v>
+        <v>0.288</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2.085</v>
+        <v>0.306</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5696,39 +5700,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.4</v>
+        <v>0.79</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.0123</v>
+        <v>-0.0186</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1337700</v>
+        <v>1554000</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="H117" t="n">
-        <v>32.46</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.04000000000001</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.42</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.439</v>
+        <v>0.626</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5741,40 +5745,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.28</v>
+        <v>0.33</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0791</v>
+        <v>-0.0571</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1325300</v>
+        <v>1548000</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.51</v>
+        <v>0.16</v>
       </c>
       <c r="H118" t="n">
-        <v>57.85</v>
+        <v>60.72</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J118" s="2" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>1.155</v>
-      </c>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="n"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
     </row>
@@ -5786,28 +5786,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>-0.0761</v>
+        <v>0.68</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.0462</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1279900</v>
+        <v>1518800</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.37</v>
+        <v>0.68</v>
       </c>
       <c r="H119" t="n">
-        <v>55.26</v>
+        <v>64.78</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.418</v>
+        <v>0.627</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.371</v>
+        <v>0.534</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5831,39 +5831,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>-0.0345</v>
+        <v>0.34</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1265100</v>
+        <v>1484100</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.2</v>
+        <v>3.15</v>
       </c>
       <c r="H120" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.77</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.301</v>
+        <v>0.314</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.298</v>
+        <v>0.316</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5876,39 +5876,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E121" s="8" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1257200</v>
+        <v>1478400</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.06</v>
+        <v>0.67</v>
       </c>
       <c r="H121" t="n">
-        <v>39.32</v>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.83</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.224</v>
+        <v>0.25</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5921,28 +5921,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.705</v>
+        <v>0.4</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>-0.0473</v>
+        <v>-0.0123</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1219200</v>
+        <v>1474100</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.39</v>
+        <v>0.96</v>
       </c>
       <c r="H122" t="n">
-        <v>40.1</v>
+        <v>32.46</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.755</v>
+        <v>0.42</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.747</v>
+        <v>0.439</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5966,28 +5966,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>-0.0545</v>
+        <v>12.94</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1187000</v>
+        <v>1455200</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H123" t="n">
-        <v>61.87</v>
+        <v>41.86</v>
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.481</v>
+        <v>13.02</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.454</v>
+        <v>13.543</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6011,28 +6011,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-0.0566</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1184700</v>
+        <v>1433500</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H124" t="n">
-        <v>54.23</v>
+        <v>60.07</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.492</v>
+        <v>1.227</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.48</v>
+        <v>1.156</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6056,28 +6056,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-0.0104</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1147200</v>
+        <v>1431600</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.47</v>
+        <v>1.84</v>
       </c>
       <c r="H125" t="n">
-        <v>45.87</v>
+        <v>37.92</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>8.715999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>8.680999999999999</v>
+        <v>0.234</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6101,28 +6101,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.585</v>
+        <v>0.61</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.025</v>
+        <v>-0.0394</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1145300</v>
+        <v>1426800</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H126" t="n">
-        <v>35.84</v>
+        <v>39.72</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.614</v>
+        <v>0.636</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.634</v>
+        <v>0.612</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6146,39 +6146,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0.0231</v>
+        <v>1.27</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-0.073</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1124000</v>
+        <v>1408500</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H127" t="n">
-        <v>62.64</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.85</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.625</v>
+        <v>1.293</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.533</v>
+        <v>1.201</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6191,39 +6191,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>3.06</v>
+        <v>0.435</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1079200</v>
+        <v>1406900</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="H128" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.23</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>3.183</v>
+        <v>0.419</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>3.379</v>
+        <v>0.371</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6236,28 +6236,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.88</v>
+        <v>0.865</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>-0.0222</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1070700</v>
+        <v>1380000</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H129" t="n">
-        <v>22.3</v>
+        <v>51.91</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.95</v>
+        <v>0.865</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.99</v>
+        <v>0.859</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6281,33 +6281,40 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.215</v>
+        <v>0.88</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.0444</v>
+        <v>-0.0222</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1053900</v>
+        <v>1369100</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.06</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>22.3</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J130" s="2" t="n"/>
-      <c r="K130" s="2" t="n"/>
+      <c r="J130" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0.99</v>
+      </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
     </row>
@@ -6319,28 +6326,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>3.27</v>
+        <v>8.5</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>-0.0239</v>
+        <v>-0.0151</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1048700</v>
+        <v>1341700</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="H131" t="n">
-        <v>32</v>
+        <v>44.97</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6348,10 +6355,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>3.449</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>3.644</v>
+        <v>8.68</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6373,19 +6380,19 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>7.69</v>
+        <v>7.62</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.0339</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1008900</v>
+        <v>1282900</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="H132" t="n">
-        <v>63.51</v>
+        <v>61.53</v>
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
@@ -6393,10 +6400,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>7.287</v>
+        <v>7.28</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>6.785</v>
+        <v>6.783</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6409,39 +6416,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.225</v>
+        <v>0.28</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.0345</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1006700</v>
+        <v>1265100</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.48</v>
+        <v>0.2</v>
       </c>
       <c r="H133" t="n">
-        <v>61.87</v>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.9</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.209</v>
+        <v>0.301</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.173</v>
+        <v>0.298</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6454,39 +6461,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1.15</v>
+        <v>0.52</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>-0.09449999999999999</v>
+        <v>-0.0545</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>993200</v>
+        <v>1255900</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="H134" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.87</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.091</v>
+        <v>0.481</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.84</v>
+        <v>0.454</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6499,28 +6506,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0.0278</v>
+        <v>2.37</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.052</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>973900</v>
+        <v>1233400</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H135" t="n">
-        <v>53.16</v>
+        <v>27.06</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6528,10 +6535,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>2.19</v>
+        <v>2.589</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2.133</v>
+        <v>2.775</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6544,39 +6551,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.705</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-0.0473</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>973000</v>
+        <v>1225800</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="H136" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="I136" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.1</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>13.018</v>
+        <v>0.755</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>13.543</v>
+        <v>0.747</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6589,39 +6596,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0566</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>968900</v>
+        <v>1192800</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H137" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.23</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.267</v>
+        <v>0.492</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1.316</v>
+        <v>0.48</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6634,39 +6641,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>LBS</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1.18</v>
+        <v>0.37</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>-0.0484</v>
+        <v>-0.0263</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>952100</v>
+        <v>1113900</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.16</v>
+        <v>0.91</v>
       </c>
       <c r="H138" t="n">
-        <v>52.57</v>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.01</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.161</v>
+        <v>0.384</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1.169</v>
+        <v>0.395</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6679,28 +6686,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.64</v>
+        <v>3.08</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0464</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>860000</v>
+        <v>1105600</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H139" t="n">
-        <v>52.95</v>
+        <v>39.01</v>
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
@@ -6708,10 +6715,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.638</v>
+        <v>3.185</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.603</v>
+        <v>3.38</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6724,28 +6731,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.585</v>
+        <v>1.16</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>-0.0565</v>
+        <v>-0.0866</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>848100</v>
+        <v>1096000</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="H140" t="n">
-        <v>43.84</v>
+        <v>59</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6753,10 +6760,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.612</v>
+        <v>1.092</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.607</v>
+        <v>0.84</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6769,28 +6776,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0.0262</v>
+        <v>3.27</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.0239</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>816000</v>
+        <v>1091100</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H141" t="n">
-        <v>35.69</v>
+        <v>32</v>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
@@ -6798,10 +6805,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>6.453</v>
+        <v>3.449</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>6.82</v>
+        <v>3.644</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6814,39 +6821,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2.96</v>
+        <v>1.2</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>-0.0295</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>815400</v>
+        <v>1081300</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.19</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H142" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.7</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>2.719</v>
+        <v>1.267</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>2.072</v>
+        <v>1.316</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6859,40 +6866,33 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.535</v>
+        <v>0.215</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>-0.0183</v>
+        <v>-0.0444</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>766000</v>
+        <v>1079200</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H143" t="n">
-        <v>31.42</v>
+        <v>0.06</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J143" s="2" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>0.62</v>
-      </c>
+      <c r="J143" s="2" t="n"/>
+      <c r="K143" s="2" t="n"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
     </row>
@@ -6904,39 +6904,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>4.12</v>
+        <v>1.19</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>-0.055</v>
+        <v>-0.0403</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>743100</v>
+        <v>1047800</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H144" t="n">
-        <v>42.05</v>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>4.321</v>
+        <v>1.162</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>4.357</v>
+        <v>1.169</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6949,28 +6949,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.505</v>
+        <v>0.585</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>-0.0288</v>
+        <v>-0.0565</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>725200</v>
+        <v>1035700</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.62</v>
+        <v>0.26</v>
       </c>
       <c r="H145" t="n">
-        <v>41.98</v>
+        <v>43.84</v>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.523</v>
+        <v>0.612</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.533</v>
+        <v>0.607</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6994,28 +6994,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>-0.04</v>
+        <v>2.22</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>723100</v>
+        <v>1026500</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H146" t="n">
-        <v>28.47</v>
+        <v>53.16</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>2.592</v>
+        <v>2.19</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>2.775</v>
+        <v>2.133</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7039,39 +7039,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.895</v>
+        <v>0.225</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>-0.0272</v>
+        <v>-0.1</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>721700</v>
+        <v>1006700</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="H147" t="n">
-        <v>48.65</v>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.87</v>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.906</v>
+        <v>0.209</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.864</v>
+        <v>0.173</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7084,39 +7084,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>-0.0352</v>
+        <v>-0.0295</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>707400</v>
+        <v>985900</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H148" t="n">
-        <v>61.93</v>
-      </c>
-      <c r="I148" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.92</v>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>2.634</v>
+        <v>2.719</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>2.163</v>
+        <v>2.072</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7129,39 +7129,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.645</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>-0.0373</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>701800</v>
+        <v>984300</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H149" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.52</v>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.457</v>
+        <v>0.638</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>1.468</v>
+        <v>0.604</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7174,28 +7174,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>6.26</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0.0262</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>700000</v>
+        <v>942000</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="H150" t="n">
-        <v>51.91</v>
+        <v>35.69</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.865</v>
+        <v>6.453</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.859</v>
+        <v>6.82</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7219,39 +7219,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.04</v>
+        <v>0.89</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>-0.028</v>
+        <v>-0.0326</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>665900</v>
+        <v>903800</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.39</v>
+        <v>0.17</v>
       </c>
       <c r="H151" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="I151" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.01</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.058</v>
+        <v>0.906</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1.19</v>
+        <v>0.864</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7264,28 +7264,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.93</v>
+        <v>5</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0177</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>657300</v>
+        <v>895600</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.62</v>
+        <v>0.19</v>
       </c>
       <c r="H152" t="n">
-        <v>29.79</v>
+        <v>47.66</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2.187</v>
+        <v>5.045</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.308</v>
+        <v>5.058</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7309,28 +7309,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>5.03</v>
+        <v>4.13</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>-0.0118</v>
+        <v>-0.0528</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>654100</v>
+        <v>866700</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H153" t="n">
-        <v>49.42</v>
+        <v>42.35</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>5.048</v>
+        <v>4.322</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>5.058</v>
+        <v>4.357</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7354,39 +7354,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>5.9</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>-0.0216</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>649300</v>
+        <v>799800</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.92</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H154" t="n">
-        <v>60.94</v>
-      </c>
-      <c r="I154" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.8</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1</v>
+        <v>6.139</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.981</v>
+        <v>6.387</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7399,28 +7399,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.83</v>
+        <v>2.77</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>-0.0235</v>
+        <v>-0.0246</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>630100</v>
+        <v>782300</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H155" t="n">
-        <v>50.72</v>
+        <v>63.97</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.839</v>
+        <v>2.637</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.773</v>
+        <v>2.163</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7444,28 +7444,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.59</v>
+        <v>0.535</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>-0.0364</v>
+        <v>-0.0183</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>624200</v>
+        <v>766000</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H156" t="n">
-        <v>41.23</v>
+        <v>31.42</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.684</v>
+        <v>0.579</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1.652</v>
+        <v>0.62</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7489,28 +7489,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.925</v>
+        <v>0.505</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.0288</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>608400</v>
+        <v>742200</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H157" t="n">
-        <v>38.68</v>
+        <v>41.98</v>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>1.003</v>
+        <v>0.523</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1.028</v>
+        <v>0.533</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7534,28 +7534,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>-0.0636</v>
+        <v>-0.045</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>604600</v>
+        <v>735000</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="H158" t="n">
-        <v>46.13</v>
+        <v>43.46</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.659</v>
+        <v>1.111</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1.676</v>
+        <v>1.09</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7579,28 +7579,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E159" s="8" t="n">
-        <v>0</v>
+        <v>1.44</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>570000</v>
+        <v>729400</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H159" t="n">
-        <v>35.78</v>
+        <v>43.22</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7608,10 +7608,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.55</v>
+        <v>1.457</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0.58</v>
+        <v>1.468</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7624,39 +7624,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>0.895</v>
+        <v>1.05</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>-0.0272</v>
+        <v>-0.0187</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>559400</v>
+        <v>728900</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="H160" t="n">
-        <v>41.89</v>
-      </c>
-      <c r="I160" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.23</v>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.91</v>
+        <v>1.059</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>0.963</v>
+        <v>1.19</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7669,28 +7669,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>-0.0383</v>
+        <v>-0.0385</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>549500</v>
+        <v>727500</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H161" t="n">
-        <v>41.76</v>
+        <v>30.14</v>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>2.054</v>
+        <v>1.869</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>2.082</v>
+        <v>2.008</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7729,10 +7729,10 @@
         <v>-0.004500000000000001</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>539700</v>
+        <v>722800</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H162" t="n">
         <v>37.41</v>
@@ -7759,39 +7759,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>-0.0538</v>
+        <v>-0.0694</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>536800</v>
+        <v>722600</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.74</v>
+        <v>0.42</v>
       </c>
       <c r="H163" t="n">
-        <v>58.66</v>
-      </c>
-      <c r="I163" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.33</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.732</v>
+        <v>1.658</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>1.61</v>
+        <v>1.676</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7804,28 +7804,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>5.88</v>
+        <v>0.625</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>-0.0249</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>536700</v>
+        <v>718500</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.05</v>
+        <v>0.58</v>
       </c>
       <c r="H164" t="n">
-        <v>32.08</v>
+        <v>37.25</v>
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>6.137</v>
+        <v>0.632</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>6.387</v>
+        <v>0.63</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7849,28 +7849,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>-0.0455</v>
+        <v>-0.06280000000000001</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>534800</v>
+        <v>716500</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1.09</v>
+        <v>0.67</v>
       </c>
       <c r="H165" t="n">
-        <v>35.68</v>
+        <v>30.19</v>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>2.264</v>
+        <v>2.188</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>2.221</v>
+        <v>2.308</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7894,39 +7894,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0.0167</v>
+        <v>1.6</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>533300</v>
+        <v>706300</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="H166" t="n">
-        <v>76.81999999999999</v>
-      </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.99</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.548</v>
+        <v>1.685</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0.514</v>
+        <v>1.653</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7939,28 +7939,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>-0.06150000000000001</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>529800</v>
+        <v>704400</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="H167" t="n">
-        <v>15.7</v>
+        <v>39.19</v>
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
@@ -7968,10 +7968,10 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>1.016</v>
+        <v>1.003</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>1.112</v>
+        <v>1.028</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7984,28 +7984,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>-0.0435</v>
+        <v>0.745</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>0.042</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>519800</v>
+        <v>670800</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H168" t="n">
-        <v>33.76</v>
+        <v>52.64</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.958</v>
+        <v>0.735</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>1.01</v>
+        <v>0.748</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8029,28 +8029,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>-0.0541</v>
+        <v>-0.0353</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>510000</v>
+        <v>669300</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="H169" t="n">
-        <v>42.32</v>
+        <v>48.84</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>1.11</v>
+        <v>0.838</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>1.09</v>
+        <v>0.773</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8074,45 +8074,630 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>0.0221</v>
+        <v>0.535</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>509900</v>
+        <v>656500</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1.04</v>
+        <v>0.19</v>
       </c>
       <c r="H170" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I170" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.78</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.667</v>
+        <v>0.55</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>0.652</v>
+        <v>0.58</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>649300</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H171" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>627600</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H172" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>2.221</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>-0.0326</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>621600</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H173" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>603200</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>-0.0383</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>597000</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H175" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>2.054</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>2.082</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>-0.0333</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>592900</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H176" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>3.159</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>-0.0503</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>551300</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H177" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>-0.0538</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>546000</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H178" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="I178" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>1.732</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>-0.0321</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>537600</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H179" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5109</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>YTLREIT</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>537300</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H180" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0308</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>KTI</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>531200</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H181" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>529300</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H182" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>519800</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H183" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M170"/>
+  <autoFilter ref="A1:M183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
+++ b/docs/downloads/2026-10-13/bursa-report-2026-10-13.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-13" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-13'!$A$1:$M$226</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,9 +82,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M223"/>
+  <dimension ref="A1:M226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,28 +543,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.155</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.1389</v>
+        <v>-0.1765</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>69082100</v>
+        <v>78529800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="H2" t="n">
-        <v>48.11</v>
+        <v>22.22</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.133</v>
+        <v>0.385</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,28 +588,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.1765</v>
+        <v>-0.1389</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>67931700</v>
+        <v>69127100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.16</v>
+        <v>1.06</v>
       </c>
       <c r="H3" t="n">
-        <v>22.22</v>
+        <v>48.11</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.385</v>
+        <v>0.133</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-0.0673</v>
+        <v>0.845</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>41758900</v>
+        <v>44269300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.29</v>
+        <v>0.61</v>
       </c>
       <c r="H4" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.56</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.49</v>
+        <v>0.788</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.48</v>
+        <v>0.714</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.0059</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>41340600</v>
+        <v>41988900</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.57</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="n">
-        <v>62.49</v>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.22</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.788</v>
+        <v>0.49</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.714</v>
+        <v>0.48</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -738,15 +738,15 @@
         <v>-0.0435</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>38530400</v>
+        <v>40379100</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H6" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -779,19 +779,19 @@
       <c r="D7" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>33901400</v>
+        <v>35011300</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H7" t="n">
         <v>70.36</v>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -828,15 +828,15 @@
         <v>-0.0142</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>29868300</v>
+        <v>30090100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H8" t="n">
         <v>72.22</v>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -867,19 +867,19 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.18</v>
+        <v>0.185</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.075</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>22033400</v>
+        <v>22103300</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.96</v>
       </c>
       <c r="H9" t="n">
-        <v>43.31</v>
+        <v>45.53</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -912,27 +912,27 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.008</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17424200</v>
+        <v>17429700</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.67</v>
       </c>
       <c r="H10" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.585</v>
+        <v>0.586</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0.51</v>
@@ -963,7 +963,7 @@
         <v>-0.0253</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>17282300</v>
+        <v>17356700</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0.98</v>
@@ -971,7 +971,7 @@
       <c r="H11" t="n">
         <v>57.58</v>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1008,15 +1008,15 @@
         <v>-0.0794</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>16901700</v>
+        <v>17072900</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>52.49</v>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1061,7 +1061,7 @@
       <c r="H13" t="n">
         <v>46.92</v>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1094,11 +1094,11 @@
       <c r="D14" s="2" t="n">
         <v>0.155</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>16122000</v>
+        <v>16142000</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.49</v>
@@ -1106,7 +1106,7 @@
       <c r="H14" t="n">
         <v>46.1</v>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1139,11 +1139,11 @@
       <c r="D15" s="2" t="n">
         <v>0.315</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>14754900</v>
+        <v>14760100</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.78</v>
@@ -1151,7 +1151,7 @@
       <c r="H15" t="n">
         <v>61.95</v>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1182,27 +1182,27 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.4</v>
+        <v>0.405</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.1398</v>
+        <v>-0.129</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>14152900</v>
+        <v>14163400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="H16" t="n">
-        <v>58.92</v>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
+        <v>60.08</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0.35</v>
@@ -1233,10 +1233,10 @@
         <v>-0.2181</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>13687900</v>
+        <v>14042900</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3.54</v>
+        <v>3.63</v>
       </c>
       <c r="H17" t="n">
         <v>20.24</v>
@@ -1278,10 +1278,10 @@
         <v>-0.06900000000000001</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>12245200</v>
+        <v>12762600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H18" t="n">
         <v>40.94</v>
@@ -1323,12 +1323,12 @@
         <v>-0.02</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>12146800</v>
+        <v>12384000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
+        <v>0.35</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1361,15 +1361,15 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>11751400</v>
+        <v>12166400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="H20" t="n">
         <v>50.45</v>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1391,39 +1391,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
+        <v>0.105</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11575600</v>
+        <v>11585000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.73</v>
+        <v>1.75</v>
       </c>
       <c r="H21" t="n">
-        <v>58.27</v>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.13</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.0455</v>
+        <v>0.82</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>11575000</v>
+        <v>11576100</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.75</v>
+        <v>0.73</v>
       </c>
       <c r="H22" t="n">
-        <v>37.13</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.114</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.122</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1496,7 +1496,7 @@
         <v>-0.0334</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>11545900</v>
+        <v>11560200</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0.46</v>
@@ -1504,7 +1504,7 @@
       <c r="H23" t="n">
         <v>52.4</v>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1526,28 +1526,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.0127</v>
+        <v>-0.0526</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>11034900</v>
+        <v>11219900</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.99</v>
+        <v>0.3</v>
       </c>
       <c r="H24" t="n">
-        <v>33.82</v>
+        <v>24.17</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.401</v>
+        <v>0.54</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.409</v>
+        <v>0.737</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,28 +1571,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.0127</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>11018700</v>
+        <v>11064600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.29</v>
+        <v>0.99</v>
       </c>
       <c r="H25" t="n">
-        <v>24.17</v>
+        <v>33.82</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.54</v>
+        <v>0.401</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.737</v>
+        <v>0.409</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
       <c r="D26" s="2" t="n">
         <v>0.155</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
@@ -1639,7 +1639,7 @@
       <c r="H26" t="n">
         <v>52.49</v>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1676,15 +1676,15 @@
         <v>0.3333</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10511100</v>
+        <v>10531200</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="H27" t="n">
         <v>63.51</v>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1717,11 +1717,11 @@
       <c r="D28" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9317800</v>
+        <v>9330200</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>1.24</v>
@@ -1729,7 +1729,7 @@
       <c r="H28" t="n">
         <v>60.4</v>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1774,7 +1774,7 @@
       <c r="H29" t="n">
         <v>50.05</v>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1811,7 +1811,7 @@
         <v>-0.1014</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9213400</v>
+        <v>9217200</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>1.09</v>
@@ -1856,15 +1856,15 @@
         <v>-0.0345</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9028600</v>
+        <v>9188400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H31" t="n">
         <v>56.03</v>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1901,7 +1901,7 @@
         <v>-0.0159</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8402500</v>
+        <v>8412500</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0.79</v>
@@ -1909,7 +1909,7 @@
       <c r="H32" t="n">
         <v>54.39</v>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1940,19 +1940,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7.44</v>
+        <v>7.45</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.0262</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8225500</v>
+        <v>8303300</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0.59</v>
       </c>
       <c r="H33" t="n">
-        <v>41.19</v>
+        <v>41.65</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.621</v>
+        <v>7.622</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>7.726</v>
@@ -1991,10 +1991,10 @@
         <v>-0.0286</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8033000</v>
+        <v>8281200</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="H34" t="n">
         <v>37.38</v>
@@ -2066,28 +2066,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.5</v>
+        <v>1.27</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.0741</v>
+        <v>-0.1477</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>7576600</v>
+        <v>7600400</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.98</v>
+        <v>4.31</v>
       </c>
       <c r="H36" t="n">
-        <v>43.62</v>
+        <v>20.15</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.52</v>
+        <v>1.486</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.53</v>
+        <v>1.611</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2111,28 +2111,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.1477</v>
+        <v>-0.0741</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>7266900</v>
+        <v>7576600</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>4.12</v>
+        <v>0.98</v>
       </c>
       <c r="H37" t="n">
-        <v>20.15</v>
+        <v>43.62</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.486</v>
+        <v>0.52</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.611</v>
+        <v>0.53</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         <v>-0.0667</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>7254000</v>
+        <v>7314400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H38" t="n">
         <v>47.07</v>
@@ -2201,28 +2201,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1.18</v>
+        <v>0.47</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.1376</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>7024800</v>
+        <v>7182000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.86</v>
+        <v>1.29</v>
       </c>
       <c r="H39" t="n">
-        <v>27.69</v>
+        <v>22.12</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.275</v>
+        <v>0.58</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1.378</v>
+        <v>0.637</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2246,28 +2246,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.475</v>
+        <v>1.18</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-0.1284</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6994900</v>
+        <v>7180100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="H40" t="n">
-        <v>22.59</v>
+        <v>27.69</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.581</v>
+        <v>1.275</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.637</v>
+        <v>1.378</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         <v>-0.0333</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>6968200</v>
+        <v>7159800</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H41" t="n">
         <v>27.94</v>
@@ -2345,19 +2345,19 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.1667</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>6884800</v>
+        <v>6924700</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H42" t="n">
-        <v>33.59</v>
+        <v>37.28</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>0.05</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>6747300</v>
+        <v>6751900</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>1.14</v>
@@ -2404,7 +2404,7 @@
       <c r="H43" t="n">
         <v>73.67</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2441,10 +2441,10 @@
         <v>-0.028</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>6340700</v>
+        <v>6457000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H44" t="n">
         <v>45.74</v>
@@ -2486,15 +2486,15 @@
         <v>0.0263</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>6269500</v>
+        <v>6427400</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H45" t="n">
         <v>44.19</v>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2525,19 +2525,19 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.0506</v>
+        <v>-0.0562</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>6183500</v>
+        <v>6207800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H46" t="n">
-        <v>41.62</v>
+        <v>40.63</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.748</v>
+        <v>1.747</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.777</v>
+        <v>1.776</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2570,19 +2570,19 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>-0.0211</v>
+        <v>-0.0246</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>6151500</v>
+        <v>6153100</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>0.43</v>
       </c>
       <c r="H47" t="n">
-        <v>51.32</v>
+        <v>50.54</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.795</v>
+        <v>2.794</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>2.702</v>
@@ -2621,15 +2621,15 @@
         <v>0.0204</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>5857400</v>
+        <v>5958400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="H48" t="n">
         <v>58.46</v>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2660,19 +2660,19 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-0.0556</v>
+        <v>-0.0519</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>5701200</v>
+        <v>5750500</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H49" t="n">
-        <v>45.7</v>
+        <v>46.33</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.621</v>
+        <v>2.622</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2.584</v>
+        <v>2.585</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2696,39 +2696,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.41</v>
+        <v>2.07</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-0.0989</v>
+        <v>-0.0417</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>5676500</v>
+        <v>5706800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.82</v>
+        <v>0.39</v>
       </c>
       <c r="H50" t="n">
-        <v>47.64</v>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.93</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.425</v>
+        <v>2.212</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.413</v>
+        <v>2.216</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2741,39 +2741,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.125</v>
+        <v>0.415</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.08789999999999999</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>5627000</v>
+        <v>5700300</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>2.93</v>
+        <v>0.82</v>
       </c>
       <c r="H51" t="n">
-        <v>54.63</v>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
+        <v>48.81</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.042</v>
+        <v>0.425</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.047</v>
+        <v>0.413</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2786,39 +2786,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0417</v>
+        <v>0.045</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.125</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>5620600</v>
+        <v>5631400</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.38</v>
+        <v>2.93</v>
       </c>
       <c r="H52" t="n">
-        <v>36.93</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.63</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.212</v>
+        <v>0.042</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.216</v>
+        <v>0.047</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.91</v>
+        <v>0.905</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.057</v>
+        <v>-0.0622</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>5594300</v>
+        <v>5620300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H53" t="n">
-        <v>47.04</v>
+        <v>46.41</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2876,28 +2876,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.31</v>
+        <v>0.31</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>-0.0438</v>
+        <v>-0.0746</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>5365600</v>
+        <v>5410000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1.77</v>
+        <v>0.91</v>
       </c>
       <c r="H54" t="n">
-        <v>63.23</v>
+        <v>42.6</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.244</v>
+        <v>0.325</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.018</v>
+        <v>0.339</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2921,28 +2921,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.66</v>
+        <v>1.31</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.0833</v>
+        <v>-0.0438</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>5287200</v>
+        <v>5378800</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.58</v>
+        <v>1.77</v>
       </c>
       <c r="H55" t="n">
-        <v>50.46</v>
+        <v>63.23</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.671</v>
+        <v>1.244</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.61</v>
+        <v>1.018</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2966,28 +2966,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.66</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.0833</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>5239900</v>
+        <v>5361300</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="H56" t="n">
-        <v>31.23</v>
+        <v>50.46</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7.577</v>
+        <v>0.671</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>8.071</v>
+        <v>0.61</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3011,28 +3011,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-0.0746</v>
+        <v>7.33</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>5210000</v>
+        <v>5248100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="H57" t="n">
-        <v>42.6</v>
+        <v>32.51</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.325</v>
+        <v>7.579</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.339</v>
+        <v>8.071999999999999</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
         <v>-0.0723</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>5138900</v>
+        <v>5151900</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0.41</v>
@@ -3079,7 +3079,7 @@
       <c r="H58" t="n">
         <v>50.53</v>
       </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="I58" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3112,7 +3112,7 @@
       <c r="D59" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="E59" s="9" t="n">
+      <c r="E59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
@@ -3155,19 +3155,19 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.0474</v>
+        <v>-0.0491</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>5059500</v>
+        <v>5120600</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H60" t="n">
-        <v>44.46</v>
+        <v>44.15</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5.625</v>
+        <v>5.624</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>5.334</v>
@@ -3206,7 +3206,7 @@
         <v>-0.1389</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>4914200</v>
+        <v>4915200</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>1.5</v>
@@ -3251,10 +3251,10 @@
         <v>-0.04</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>4841500</v>
+        <v>4873300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H62" t="n">
         <v>29.38</v>
@@ -3281,28 +3281,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.61</v>
+        <v>0.22</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.0394</v>
+        <v>-0.0222</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>4791400</v>
+        <v>4804400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1.84</v>
+        <v>0.19</v>
       </c>
       <c r="H63" t="n">
-        <v>39.72</v>
+        <v>31.58</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.636</v>
+        <v>0.246</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.612</v>
+        <v>0.301</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3326,28 +3326,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E64" s="9" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>4760800</v>
+        <v>4801400</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.18</v>
+        <v>1.85</v>
       </c>
       <c r="H64" t="n">
-        <v>33.08</v>
+        <v>41.62</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.247</v>
+        <v>0.636</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.301</v>
+        <v>0.612</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3371,39 +3371,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.275</v>
+        <v>6.42</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0678</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>4667200</v>
+        <v>4679000</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.54</v>
+        <v>0.95</v>
       </c>
       <c r="H65" t="n">
-        <v>47.72</v>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
+        <v>59.19</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.278</v>
+        <v>5.894</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.302</v>
+        <v>5.8</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3416,39 +3416,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.019</v>
+        <v>0.275</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.0678</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>4642100</v>
+        <v>4674200</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="H66" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.72</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.514</v>
+        <v>0.278</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.44</v>
+        <v>0.302</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3461,39 +3461,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>-0.0575</v>
+        <v>0.535</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.019</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>4620600</v>
+        <v>4647100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="H67" t="n">
-        <v>58.66</v>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>5.892</v>
+        <v>0.514</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>5.799</v>
+        <v>0.44</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>-0.0455</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>4493700</v>
+        <v>4543700</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>0.29</v>
@@ -3553,19 +3553,19 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.033</v>
+        <v>-0.0354</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>4362400</v>
+        <v>4403100</v>
       </c>
       <c r="G69" s="5" t="n">
         <v>0.51</v>
       </c>
       <c r="H69" t="n">
-        <v>58.45</v>
+        <v>58.06</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>3.978</v>
+        <v>3.977</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>3.465</v>
@@ -3589,28 +3589,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E70" s="9" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>4348900</v>
+        <v>4368800</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="H70" t="n">
-        <v>58.7</v>
+        <v>39.71</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.369</v>
+        <v>1.316</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.368</v>
+        <v>1.307</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3634,39 +3634,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>4333300</v>
+        <v>4353400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.57</v>
+        <v>0.32</v>
       </c>
       <c r="H71" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.24</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>4.367</v>
+        <v>0.772</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>4.458</v>
+        <v>0.716</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3679,39 +3679,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0062</v>
+        <v>0.375</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>4326400</v>
+        <v>4348900</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="H72" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.7</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.772</v>
+        <v>0.369</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.716</v>
+        <v>0.368</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3724,28 +3724,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.24</v>
+        <v>0.195</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>-0.0388</v>
+        <v>-0.025</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>4315800</v>
+        <v>4343200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.43</v>
+        <v>1.05</v>
       </c>
       <c r="H73" t="n">
-        <v>38.61</v>
+        <v>38.63</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.315</v>
+        <v>0.206</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.307</v>
+        <v>0.208</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3769,28 +3769,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>-0.025</v>
+        <v>4.31</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>4293200</v>
+        <v>4337900</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1.04</v>
+        <v>0.57</v>
       </c>
       <c r="H74" t="n">
-        <v>38.63</v>
+        <v>46.4</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.206</v>
+        <v>4.367</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.208</v>
+        <v>4.458</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         <v>-0.0247</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>4274000</v>
+        <v>4323000</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H75" t="n">
         <v>34.48</v>
@@ -3859,39 +3859,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0176</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KRONO</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>-0.1034</v>
+        <v>10.02</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>4257700</v>
+        <v>4298200</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.09</v>
+        <v>0.33</v>
       </c>
       <c r="H76" t="n">
-        <v>45.32</v>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.36</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.138</v>
+        <v>10.022</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.132</v>
+        <v>10.203</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3904,39 +3904,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0176</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>KRONO</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.0234</v>
+        <v>0.13</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.1034</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>4169400</v>
+        <v>4257700</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.32</v>
+        <v>1.09</v>
       </c>
       <c r="H77" t="n">
-        <v>48.51</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.32</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>10.024</v>
+        <v>0.138</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>10.203</v>
+        <v>0.132</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3949,28 +3949,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.68</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.0556</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>4073200</v>
+        <v>4188300</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="H78" t="n">
-        <v>55.76</v>
+        <v>26.68</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>3.604</v>
+        <v>0.749</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.785</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3994,39 +3994,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>-0.0175</v>
+        <v>0.22</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>4064300</v>
+        <v>4105800</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.44</v>
+        <v>0.19</v>
       </c>
       <c r="H79" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.61</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.781</v>
+        <v>0.225</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2.611</v>
+        <v>0.241</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4039,39 +4039,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.83</v>
+        <v>2.81</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>-0.0119</v>
+        <v>-0.0175</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>4043100</v>
+        <v>4083200</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>5.69</v>
+        <v>0.44</v>
       </c>
       <c r="H80" t="n">
-        <v>32.27</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.3</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.856</v>
+        <v>2.781</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.864</v>
+        <v>2.611</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4084,28 +4084,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.22</v>
+        <v>3.68</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>3940000</v>
+        <v>4079900</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="H81" t="n">
-        <v>43.61</v>
+        <v>55.76</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.225</v>
+        <v>3.604</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.241</v>
+        <v>2.785</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4129,39 +4129,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.08529999999999999</v>
+        <v>-0.0119</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>3905700</v>
+        <v>4044900</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1</v>
+        <v>5.69</v>
       </c>
       <c r="H82" t="n">
-        <v>49.86</v>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.27</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.596</v>
+        <v>0.856</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.582</v>
+        <v>0.864</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4174,39 +4174,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.435</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.0486</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>3903200</v>
+        <v>4016600</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.63</v>
+        <v>0.38</v>
       </c>
       <c r="H83" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.43</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.428</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4219,39 +4219,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>5.49</v>
+        <v>0.14</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0667</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3871300</v>
+        <v>3994000</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="n">
-        <v>51.47</v>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
+        <v>66.91</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5.479</v>
+        <v>0.119</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>5.366</v>
+        <v>0.095</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4264,39 +4264,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.435</v>
+        <v>5.48</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.0712</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>3799400</v>
+        <v>3930500</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.36</v>
+        <v>1.12</v>
       </c>
       <c r="H85" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I85" s="8" t="inlineStr">
+        <v>51.24</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.45</v>
+        <v>5.478</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.428</v>
+        <v>5.366</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4309,39 +4309,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>3757200</v>
+        <v>3921700</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="H86" t="n">
-        <v>43.24</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.86</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.456</v>
+        <v>0.596</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.422</v>
+        <v>0.582</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4363,19 +4363,19 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>-0.045</v>
+        <v>-0.0415</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>3735400</v>
+        <v>3775000</v>
       </c>
       <c r="G87" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="H87" t="n">
-        <v>41.52</v>
+        <v>41.91</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.947</v>
+        <v>2.948</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>2.833</v>
@@ -4399,28 +4399,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.79</v>
+        <v>0.425</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>-0.0539</v>
+        <v>-0.0761</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>3687100</v>
+        <v>3762700</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.57</v>
+        <v>1.04</v>
       </c>
       <c r="H88" t="n">
-        <v>61.36</v>
+        <v>41.9</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.754</v>
+        <v>0.455</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.668</v>
+        <v>0.422</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4444,39 +4444,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.0571</v>
+        <v>0.79</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.0539</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>3655400</v>
+        <v>3690500</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="H89" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.165</v>
+        <v>0.754</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.166</v>
+        <v>0.668</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4489,39 +4489,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E90" s="9" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>3600100</v>
+        <v>3655400</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.37</v>
+        <v>0.68</v>
       </c>
       <c r="H90" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.31999999999999</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.162</v>
+        <v>0.165</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.122</v>
+        <v>0.166</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
         <v>-0.0649</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>3599200</v>
+        <v>3613200</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>0.43</v>
@@ -4579,28 +4579,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>-0.0438</v>
+        <v>1.15</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>3530600</v>
+        <v>3600100</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="H92" t="n">
-        <v>46.94</v>
+        <v>49.32</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.778</v>
+        <v>1.162</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.773</v>
+        <v>1.122</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4633,19 +4633,19 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.0339</v>
+        <v>-0.0395</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>3500600</v>
+        <v>3545900</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H93" t="n">
-        <v>34.86</v>
+        <v>34.09</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.813</v>
+        <v>1.812</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>1.921</v>
@@ -4669,28 +4669,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.06</v>
+        <v>0.765</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-0.0702</v>
+        <v>-0.0438</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>3397100</v>
+        <v>3530600</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="H94" t="n">
-        <v>52.62</v>
+        <v>46.94</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.07</v>
+        <v>0.778</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.925</v>
+        <v>0.773</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4714,39 +4714,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.57</v>
+        <v>1.07</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0579</v>
+        <v>-0.0614</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>3376200</v>
+        <v>3518000</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="H95" t="n">
-        <v>58.26</v>
-      </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.551</v>
+        <v>1.071</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.497</v>
+        <v>0.925</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4759,39 +4759,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.145</v>
+        <v>0.57</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.0333</v>
+        <v>-0.0579</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>3350000</v>
+        <v>3376200</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="H96" t="n">
-        <v>71.08</v>
-      </c>
-      <c r="I96" s="8" t="inlineStr">
+        <v>58.26</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.12</v>
+        <v>0.551</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.095</v>
+        <v>0.497</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4827,7 +4827,7 @@
       <c r="H97" t="n">
         <v>67.25</v>
       </c>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="I97" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4864,10 +4864,10 @@
         <v>-0.0526</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>3153900</v>
+        <v>3186300</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="H98" t="n">
         <v>23.28</v>
@@ -4909,7 +4909,7 @@
         <v>-0.0566</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>3153100</v>
+        <v>3163400</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>0.44</v>
@@ -4948,19 +4948,19 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1014</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>3074100</v>
+        <v>3077800</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>0.68</v>
       </c>
       <c r="H100" t="n">
-        <v>26.33</v>
+        <v>25.19</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4984,28 +4984,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2.77</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.061</v>
+        <v>-0.0278</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>3007300</v>
+        <v>3074600</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="H101" t="n">
-        <v>34.88</v>
+        <v>42.66</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.956</v>
+        <v>8.702</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>3.03</v>
+        <v>8.678000000000001</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5029,28 +5029,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.032</v>
+        <v>-0.061</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2995700</v>
+        <v>3064700</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H102" t="n">
-        <v>29.5</v>
+        <v>34.88</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2.594</v>
+        <v>2.956</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.776</v>
+        <v>3.03</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5074,39 +5074,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0.0501</v>
+        <v>2.42</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.032</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>2957300</v>
+        <v>3025200</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.84</v>
+        <v>0.57</v>
       </c>
       <c r="H103" t="n">
-        <v>56.55</v>
-      </c>
-      <c r="I103" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.5</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>7.755</v>
+        <v>2.594</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>7.899</v>
+        <v>2.776</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5119,39 +5119,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>-0.07690000000000001</v>
+        <v>2.13</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>2911200</v>
+        <v>2962300</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1.81</v>
+        <v>0.15</v>
       </c>
       <c r="H104" t="n">
-        <v>33.68</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.85</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.262</v>
+        <v>2.104</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.277</v>
+        <v>2.085</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5164,39 +5164,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E105" s="9" t="n">
-        <v>0</v>
+        <v>7.97</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0.0501</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>2878300</v>
+        <v>2960400</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="H105" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.55</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.295</v>
+        <v>7.755</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.296</v>
+        <v>7.899</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5209,28 +5209,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.029</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>2865200</v>
+        <v>2935900</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="H106" t="n">
-        <v>42.46</v>
+        <v>33.68</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>8.701000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>8.677</v>
+        <v>0.277</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5254,39 +5254,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>-0.044</v>
+        <v>0.295</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2852400</v>
+        <v>2878400</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.68</v>
+        <v>0.99</v>
       </c>
       <c r="H107" t="n">
-        <v>61.26</v>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>7.279</v>
+        <v>0.295</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>6.783</v>
+        <v>0.296</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5299,39 +5299,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.59</v>
+        <v>7.62</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>-0.0167</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>2783200</v>
+        <v>2860200</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1.15</v>
+        <v>0.68</v>
       </c>
       <c r="H108" t="n">
-        <v>37.34</v>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.53</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.614</v>
+        <v>7.28</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.634</v>
+        <v>6.783</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5344,28 +5344,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>3.02</v>
+        <v>0.585</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.0563</v>
+        <v>-0.025</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>2740000</v>
+        <v>2792300</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.88</v>
+        <v>1.16</v>
       </c>
       <c r="H109" t="n">
-        <v>53.1</v>
+        <v>35.84</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>3.002</v>
+        <v>0.614</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2.813</v>
+        <v>0.634</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5389,39 +5389,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>3.02</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0563</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>2738200</v>
+        <v>2771500</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.14</v>
+        <v>0.89</v>
       </c>
       <c r="H110" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="I110" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.1</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.105</v>
+        <v>3.002</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2.085</v>
+        <v>2.813</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5434,39 +5434,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.98</v>
+        <v>12.98</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>0.0102</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>2721300</v>
+        <v>2750600</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.84</v>
+        <v>0.3</v>
       </c>
       <c r="H111" t="n">
-        <v>79.52</v>
-      </c>
-      <c r="I111" s="8" t="inlineStr">
+        <v>43.82</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.679</v>
+        <v>13.023</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2.31</v>
+        <v>13.544</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5479,39 +5479,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>-0.0062</v>
+        <v>2.98</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0.0102</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>2683300</v>
+        <v>2727400</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1.32</v>
+        <v>0.84</v>
       </c>
       <c r="H112" t="n">
-        <v>58.26</v>
-      </c>
-      <c r="I112" s="8" t="inlineStr">
+        <v>79.52</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.773</v>
+        <v>2.679</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.762</v>
+        <v>2.31</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5524,39 +5524,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>2.46</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>2678600</v>
+        <v>2707000</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H113" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="I113" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.61</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>13.025</v>
+        <v>2.462</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>13.545</v>
+        <v>2.352</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2.46</v>
+        <v>0.795</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.012</v>
+        <v>-0.0124</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>2633200</v>
+        <v>2703300</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.2</v>
+        <v>1.33</v>
       </c>
       <c r="H114" t="n">
-        <v>52.61</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.81</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>2.462</v>
+        <v>0.773</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>2.352</v>
+        <v>0.762</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5682,7 +5682,7 @@
       <c r="H116" t="n">
         <v>47.48</v>
       </c>
-      <c r="I116" s="8" t="inlineStr">
+      <c r="I116" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -5704,28 +5704,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.3</v>
+        <v>5.89</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.0299</v>
+        <v>-0.0232</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>2595900</v>
+        <v>2603200</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.9</v>
+        <v>0.22</v>
       </c>
       <c r="H117" t="n">
-        <v>46.17</v>
+        <v>32.44</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.345</v>
+        <v>6.138</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.245</v>
+        <v>6.387</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5749,28 +5749,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.455</v>
+        <v>1.3</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0421</v>
+        <v>-0.0299</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>2588800</v>
+        <v>2600600</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>1.38</v>
+        <v>0.9</v>
       </c>
       <c r="H118" t="n">
-        <v>48.6</v>
+        <v>46.17</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.46</v>
+        <v>1.345</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.461</v>
+        <v>1.245</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5803,27 +5803,27 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-0.0127</v>
+        <v>-0.0102</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>2568800</v>
+        <v>2595400</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="H119" t="n">
-        <v>54.14</v>
-      </c>
-      <c r="I119" s="8" t="inlineStr">
+        <v>54.73</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>3.865</v>
+        <v>3.866</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>3.59</v>
@@ -5839,28 +5839,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>5.9</v>
+        <v>0.455</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>-0.0216</v>
+        <v>-0.0421</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>2565100</v>
+        <v>2590800</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.22</v>
+        <v>1.38</v>
       </c>
       <c r="H120" t="n">
-        <v>32.8</v>
+        <v>48.6</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>6.139</v>
+        <v>0.46</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>6.387</v>
+        <v>0.461</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5893,27 +5893,27 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>10.74</v>
+        <v>10.72</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-0.0236</v>
+        <v>-0.0255</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>2496500</v>
+        <v>2513700</v>
       </c>
       <c r="G121" s="5" t="n">
         <v>0.74</v>
       </c>
       <c r="H121" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="I121" s="8" t="inlineStr">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>10.282</v>
+        <v>10.28</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>9.555999999999999</v>
@@ -5929,39 +5929,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>-0.0495</v>
+        <v>6.27</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0.0279</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>2447500</v>
+        <v>2479100</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="H122" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.34</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>6.454</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.493</v>
+        <v>6.82</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5974,39 +5974,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0.0279</v>
+        <v>0.96</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>-0.0495</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>2447400</v>
+        <v>2447500</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="H123" t="n">
-        <v>36.34</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.34999999999999</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>6.454</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>6.82</v>
+        <v>0.493</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
         <v>-0.0984</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>2440700</v>
+        <v>2440800</v>
       </c>
       <c r="G124" s="5" t="n">
         <v>0.66</v>
@@ -6042,7 +6042,7 @@
       <c r="H124" t="n">
         <v>59.84</v>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="I124" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6079,7 +6079,7 @@
         <v>-0.045</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>2380200</v>
+        <v>2380500</v>
       </c>
       <c r="G125" s="5" t="n">
         <v>0.49</v>
@@ -6109,39 +6109,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.615</v>
+        <v>0.825</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>2286100</v>
+        <v>2307000</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H126" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.19</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.613</v>
+        <v>0.826</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.599</v>
+        <v>0.762</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6169,7 +6169,7 @@
         <v>-0.0541</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>2285600</v>
+        <v>2286600</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>0.74</v>
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0.0469</v>
+        <v>0.615</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>2281200</v>
+        <v>2286100</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>4.84</v>
+        <v>0.78</v>
       </c>
       <c r="H128" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="I128" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.4</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.314</v>
+        <v>0.613</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.316</v>
+        <v>0.599</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6244,39 +6244,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E129" s="9" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0.0469</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>2244200</v>
+        <v>2281200</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>1.04</v>
+        <v>4.84</v>
       </c>
       <c r="H129" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="I129" s="8" t="inlineStr">
+        <v>67.47</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.314</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.316</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6289,39 +6289,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.635</v>
+        <v>0.74</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.1301</v>
+        <v>-0.0452</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>2231400</v>
+        <v>2258500</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.44</v>
+        <v>1.16</v>
       </c>
       <c r="H130" t="n">
-        <v>66.91</v>
-      </c>
-      <c r="I130" s="8" t="inlineStr">
+        <v>56.14</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.532</v>
+        <v>0.715</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.448</v>
+        <v>0.694</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6334,39 +6334,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>-0.0054</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>2214600</v>
+        <v>2244200</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.42</v>
+        <v>1.04</v>
       </c>
       <c r="H131" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.28</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.908</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.865</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6379,39 +6379,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.83</v>
+        <v>0.635</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.08289999999999999</v>
+        <v>-0.1301</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>2204400</v>
+        <v>2237000</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.64</v>
+        <v>0.44</v>
       </c>
       <c r="H132" t="n">
-        <v>53.03</v>
-      </c>
-      <c r="I132" s="8" t="inlineStr">
+        <v>66.91</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.826</v>
+        <v>0.532</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.762</v>
+        <v>0.448</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6424,39 +6424,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.735</v>
+        <v>0.915</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>-0.0516</v>
+        <v>-0.0054</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>2201500</v>
+        <v>2232400</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>1.14</v>
+        <v>0.42</v>
       </c>
       <c r="H133" t="n">
-        <v>55.21</v>
-      </c>
-      <c r="I133" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.51</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.715</v>
+        <v>0.908</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.694</v>
+        <v>0.865</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6484,7 +6484,7 @@
         <v>-0.0319</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>2145500</v>
+        <v>2160500</v>
       </c>
       <c r="G134" s="5" t="n">
         <v>0.18</v>
@@ -6510,39 +6510,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.0803</v>
+        <v>-0.0242</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>2014800</v>
+        <v>2026100</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="H135" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="I135" s="8" t="inlineStr">
+        <v>56.66</v>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.292</v>
+        <v>1.164</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>1.201</v>
+        <v>1.17</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6555,39 +6555,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>-0.0242</v>
+        <v>-0.0803</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>2014500</v>
+        <v>2018400</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="H136" t="n">
-        <v>56.66</v>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
+        <v>49.08</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1.164</v>
+        <v>1.292</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1.17</v>
+        <v>1.201</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6600,39 +6600,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ESCERAM</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.215</v>
+        <v>0.68</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>0.1622</v>
+        <v>0.0462</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1979000</v>
+        <v>2017500</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="H137" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="I137" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.78</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.186</v>
+        <v>0.627</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.183</v>
+        <v>0.534</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6645,39 +6645,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>ESCERAM</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>-0.0711</v>
+        <v>0.215</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0.1622</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1931500</v>
+        <v>1979000</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.82</v>
+        <v>1.8</v>
       </c>
       <c r="H138" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.75</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2.112</v>
+        <v>0.186</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1.967</v>
+        <v>0.183</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6690,28 +6690,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0462</v>
+        <v>2.08</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>-0.0756</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1928000</v>
+        <v>1932700</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="H139" t="n">
-        <v>64.78</v>
+        <v>50.56</v>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.627</v>
+        <v>2.111</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.534</v>
+        <v>1.967</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       <c r="H140" t="n">
         <v>56.8</v>
       </c>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="I140" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -6795,10 +6795,10 @@
         <v>-0.025</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1881500</v>
+        <v>1889000</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H141" t="n">
         <v>56.2</v>
@@ -6834,19 +6834,19 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.27</v>
+        <v>0.265</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>-0.0357</v>
+        <v>-0.0536</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1867700</v>
+        <v>1881600</v>
       </c>
       <c r="G142" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="H142" t="n">
-        <v>31.04</v>
+        <v>28.67</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.288</v>
+        <v>0.287</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0.306</v>
@@ -6870,39 +6870,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0222</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1784000</v>
+        <v>1836300</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H143" t="n">
-        <v>76.04000000000001</v>
-      </c>
-      <c r="I143" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.3</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0.626</v>
+        <v>0.99</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6915,28 +6915,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.425</v>
+        <v>5.03</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>-0.0761</v>
+        <v>-0.0118</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>1781500</v>
+        <v>1833900</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="H144" t="n">
-        <v>55.26</v>
+        <v>49.42</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.418</v>
+        <v>5.048</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.371</v>
+        <v>5.058</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6960,40 +6960,36 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.88</v>
+        <v>0.335</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>-0.0222</v>
+        <v>-0.0429</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>1777800</v>
+        <v>1807000</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.73</v>
+        <v>0.18</v>
       </c>
       <c r="H145" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>0.99</v>
-      </c>
+        <v>63.34</v>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n"/>
+      <c r="K145" s="2" t="n"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
     </row>
@@ -7005,36 +7001,40 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>0.335</v>
+        <v>0.79</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>-0.0429</v>
+        <v>-0.0186</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1741500</v>
+        <v>1784000</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.17</v>
+        <v>0.76</v>
       </c>
       <c r="H146" t="n">
-        <v>63.34</v>
-      </c>
-      <c r="I146" s="8" t="inlineStr">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J146" s="2" t="n"/>
-      <c r="K146" s="2" t="n"/>
+      <c r="J146" s="2" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>0.626</v>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
     </row>
@@ -7046,28 +7046,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>5.05</v>
+        <v>0.425</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>1738100</v>
+        <v>1781500</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.37</v>
+        <v>0.51</v>
       </c>
       <c r="H147" t="n">
-        <v>50.68</v>
+        <v>55.26</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>5.05</v>
+        <v>0.418</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>5.059</v>
+        <v>0.371</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
         <v>-0.0926</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>1709900</v>
+        <v>1724500</v>
       </c>
       <c r="G148" s="5" t="n">
         <v>0.38</v>
@@ -7145,19 +7145,19 @@
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.0091</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>1584100</v>
+        <v>1597700</v>
       </c>
       <c r="G149" s="5" t="n">
         <v>0.31</v>
       </c>
       <c r="H149" t="n">
-        <v>41.14</v>
+        <v>41.97</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>4.48</v>
+        <v>4.481</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>4.804</v>
@@ -7181,39 +7181,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>-0.04019999999999999</v>
+        <v>-0.033</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>1562100</v>
+        <v>1577500</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="H150" t="n">
-        <v>40.15</v>
-      </c>
-      <c r="I150" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.9</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>3.187</v>
+        <v>1.87</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>3.38</v>
+        <v>2.008</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7226,39 +7226,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0.25</v>
+        <v>3.1</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>1536900</v>
+        <v>1563800</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="H151" t="n">
-        <v>49.83</v>
-      </c>
-      <c r="I151" s="8" t="inlineStr">
+        <v>40.15</v>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.25</v>
+        <v>3.187</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0.254</v>
+        <v>3.38</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7271,39 +7271,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.74</v>
+        <v>0.25</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>-0.044</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>1484600</v>
+        <v>1538200</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H152" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="I152" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.83</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.868</v>
+        <v>0.25</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.008</v>
+        <v>0.254</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7361,39 +7361,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>FEYTECH</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>0.52</v>
+        <v>0.215</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>-0.0545</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1475300</v>
+        <v>1483100</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.36</v>
+        <v>1.91</v>
       </c>
       <c r="H154" t="n">
-        <v>61.87</v>
-      </c>
-      <c r="I154" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.92</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.481</v>
+        <v>0.23</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0.454</v>
+        <v>0.234</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7406,39 +7406,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>1.17</v>
+        <v>0.52</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0545</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1435500</v>
+        <v>1481300</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="H155" t="n">
-        <v>59.81</v>
-      </c>
-      <c r="I155" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.87</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>1.093</v>
+        <v>0.481</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.84</v>
+        <v>0.454</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7451,28 +7451,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FEYTECH</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.215</v>
+        <v>1.17</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1433100</v>
+        <v>1451200</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1.84</v>
+        <v>0.19</v>
       </c>
       <c r="H156" t="n">
-        <v>37.92</v>
+        <v>59.81</v>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
@@ -7480,10 +7480,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.23</v>
+        <v>1.093</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.234</v>
+        <v>0.84</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7511,7 +7511,7 @@
         <v>-0.0619</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>1426400</v>
+        <v>1450900</v>
       </c>
       <c r="G157" s="5" t="n">
         <v>0.47</v>
@@ -7586,39 +7586,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2.98</v>
+        <v>0.255</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>-0.023</v>
+        <v>-0.0377</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1365200</v>
+        <v>1405300</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="H159" t="n">
-        <v>65.87</v>
-      </c>
-      <c r="I159" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.13</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>2.721</v>
+        <v>0.265</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>2.072</v>
+        <v>0.233</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
         <v>-0.06</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>1358300</v>
+        <v>1377400</v>
       </c>
       <c r="G160" s="5" t="n">
         <v>0.12</v>
@@ -7674,39 +7674,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0.26</v>
+        <v>2.98</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.023</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>1340900</v>
+        <v>1369700</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H161" t="n">
-        <v>49.95</v>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.87</v>
+      </c>
+      <c r="I161" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.266</v>
+        <v>2.721</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.233</v>
+        <v>2.072</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7734,7 +7734,7 @@
         <v>-0.0444</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>1334700</v>
+        <v>1337200</v>
       </c>
       <c r="G162" s="5" t="n">
         <v>0.07000000000000001</v>
@@ -7802,28 +7802,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0.925</v>
+        <v>3.3</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>-0.0107</v>
+        <v>-0.0149</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>1296900</v>
+        <v>1313300</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.75</v>
+        <v>0.21</v>
       </c>
       <c r="H164" t="n">
-        <v>52.85</v>
+        <v>33.51</v>
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.923</v>
+        <v>3.452</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0.854</v>
+        <v>3.645</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7847,28 +7847,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E165" s="9" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>1291300</v>
+        <v>1301700</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.98</v>
+        <v>0.75</v>
       </c>
       <c r="H165" t="n">
-        <v>40.75</v>
+        <v>51.98</v>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.249</v>
+        <v>0.923</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.25</v>
+        <v>0.854</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7892,39 +7892,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0.0231</v>
+        <v>0.24</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>1286900</v>
+        <v>1293600</v>
       </c>
       <c r="G166" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H166" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="K166" s="2" t="n">
         <v>0.25</v>
-      </c>
-      <c r="H166" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>2.189</v>
-      </c>
-      <c r="K166" s="2" t="n">
-        <v>2.133</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
         <v>-0.066</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>1283300</v>
+        <v>1293300</v>
       </c>
       <c r="G167" s="5" t="n">
         <v>0.65</v>
@@ -7960,7 +7960,7 @@
       <c r="H167" t="n">
         <v>52.57</v>
       </c>
-      <c r="I167" s="8" t="inlineStr">
+      <c r="I167" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7982,28 +7982,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>-0.0119</v>
+        <v>0.535</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>1281900</v>
+        <v>1289500</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="H168" t="n">
-        <v>34.05</v>
+        <v>35.78</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>3.453</v>
+        <v>0.55</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>3.645</v>
+        <v>0.58</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8027,39 +8027,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>-0.0299</v>
+        <v>2.21</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0.0231</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>1273600</v>
+        <v>1287000</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="H169" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="I169" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.4</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.639</v>
+        <v>2.189</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.604</v>
+        <v>2.133</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8072,39 +8072,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>0.28</v>
+        <v>0.645</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>-0.0345</v>
+        <v>-0.0373</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>1265100</v>
+        <v>1282600</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H170" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.52</v>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.301</v>
+        <v>0.638</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>0.298</v>
+        <v>0.604</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8117,28 +8117,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.28</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>1207200</v>
+        <v>1265100</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H171" t="n">
-        <v>47.08</v>
+        <v>29.9</v>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>1.928</v>
+        <v>0.301</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>1.956</v>
+        <v>0.298</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8162,39 +8162,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>-0.08</v>
+        <v>1.92</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>1169400</v>
+        <v>1223100</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H172" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="I172" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.08</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.209</v>
+        <v>1.928</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>0.173</v>
+        <v>1.956</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8207,39 +8207,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>0.76</v>
+        <v>0.23</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>-0.0194</v>
+        <v>-0.08</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>1163500</v>
+        <v>1212700</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H173" t="n">
-        <v>45.07</v>
-      </c>
-      <c r="I173" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.83</v>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.77</v>
+        <v>0.209</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0.768</v>
+        <v>0.173</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8252,28 +8252,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>2.79</v>
+        <v>0.22</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>-0.0176</v>
+        <v>-0.0435</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>1150500</v>
+        <v>1193800</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="H174" t="n">
-        <v>65.41</v>
+        <v>52.67</v>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>2.639</v>
+        <v>0.219</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>2.164</v>
+        <v>0.207</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="7" t="inlineStr"/>
@@ -8297,39 +8297,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>0.62</v>
+        <v>5.5</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.0036</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>1149200</v>
+        <v>1170100</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1.9</v>
+        <v>0.75</v>
       </c>
       <c r="H175" t="n">
-        <v>78.34</v>
-      </c>
-      <c r="I175" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.69</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.549</v>
+        <v>5.692</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>0.514</v>
+        <v>5.859</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8342,28 +8342,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0.585</v>
+        <v>0.76</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>-0.0565</v>
+        <v>-0.0194</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>1129500</v>
+        <v>1163600</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="H176" t="n">
-        <v>43.84</v>
+        <v>45.07</v>
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.612</v>
+        <v>0.77</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>0.607</v>
+        <v>0.768</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8387,39 +8387,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>5.5</v>
+        <v>0.615</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.025</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>1109400</v>
+        <v>1154200</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.71</v>
+        <v>1.91</v>
       </c>
       <c r="H177" t="n">
-        <v>35.69</v>
-      </c>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.61</v>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>5.692</v>
+        <v>0.549</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>5.859</v>
+        <v>0.514</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8432,28 +8432,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>HOCKSOON</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>0.205</v>
+        <v>2.79</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>-0.0682</v>
+        <v>-0.0176</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>1082200</v>
+        <v>1150500</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1.83</v>
+        <v>0.36</v>
       </c>
       <c r="H178" t="n">
-        <v>13.59</v>
+        <v>65.41</v>
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.254</v>
+        <v>2.639</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>0.288</v>
+        <v>2.164</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8477,28 +8477,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E179" s="10" t="n">
-        <v>0.028</v>
+        <v>0.585</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>-0.0565</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>1050300</v>
+        <v>1129500</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H179" t="n">
-        <v>49.75</v>
+        <v>43.84</v>
       </c>
       <c r="I179" s="6" t="inlineStr">
         <is>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.734</v>
+        <v>0.612</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>0.748</v>
+        <v>0.607</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8522,28 +8522,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>HOCKSOON</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E180" s="9" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>-0.0682</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>1038500</v>
+        <v>1116600</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.24</v>
+        <v>1.89</v>
       </c>
       <c r="H180" t="n">
-        <v>39.11</v>
+        <v>13.59</v>
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>1.456</v>
+        <v>0.254</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>1.468</v>
+        <v>0.288</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8567,39 +8567,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>-0.0204</v>
+        <v>0.735</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>0.028</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>1032800</v>
+        <v>1050300</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H181" t="n">
-        <v>59.28</v>
-      </c>
-      <c r="I181" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.75</v>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.232</v>
+        <v>0.734</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>0.204</v>
+        <v>0.748</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8612,28 +8612,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>-0.0435</v>
+        <v>1.43</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>1028800</v>
+        <v>1039100</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
       <c r="H182" t="n">
-        <v>52.67</v>
+        <v>39.11</v>
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0.219</v>
+        <v>1.456</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0.207</v>
+        <v>1.468</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8657,39 +8657,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E183" s="9" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>1018700</v>
+        <v>1032800</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="H183" t="n">
-        <v>35.78</v>
-      </c>
-      <c r="I183" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.28</v>
+      </c>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.55</v>
+        <v>0.232</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>0.58</v>
+        <v>0.204</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8702,28 +8702,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>1.58</v>
+        <v>0.31</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>-0.0424</v>
+        <v>-0.0159</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>955300</v>
+        <v>1023600</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.99</v>
+        <v>0.52</v>
       </c>
       <c r="H184" t="n">
-        <v>40.51</v>
+        <v>37.81</v>
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>1.683</v>
+        <v>0.329</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>1.652</v>
+        <v>0.33</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8762,7 +8762,7 @@
         <v>-0.004099999999999999</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>950000</v>
+        <v>964600</v>
       </c>
       <c r="G185" s="5" t="n">
         <v>0.12</v>
@@ -8792,28 +8792,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>-0.0725</v>
+        <v>-0.0424</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>875200</v>
+        <v>955300</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="H186" t="n">
-        <v>29.4</v>
+        <v>40.51</v>
       </c>
       <c r="I186" s="6" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>2.186</v>
+        <v>1.683</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>2.307</v>
+        <v>1.652</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="7" t="inlineStr"/>
@@ -8837,28 +8837,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="E187" s="10" t="n">
-        <v>0.003</v>
+        <v>1.93</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>852700</v>
+        <v>897200</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.19</v>
+        <v>0.84</v>
       </c>
       <c r="H187" t="n">
-        <v>47.91</v>
+        <v>29.79</v>
       </c>
       <c r="I187" s="6" t="inlineStr">
         <is>
@@ -8866,10 +8866,10 @@
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>6.762</v>
+        <v>2.187</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>6.845</v>
+        <v>2.308</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="7" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
         <v>-0.0105</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>845500</v>
+        <v>892300</v>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H188" t="n">
         <v>30.19</v>
@@ -8927,28 +8927,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>0.865</v>
+        <v>0.51</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>-0.0335</v>
+        <v>-0.0192</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>839500</v>
+        <v>881600</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.35</v>
+        <v>0.76</v>
       </c>
       <c r="H189" t="n">
-        <v>17.06</v>
+        <v>43.54</v>
       </c>
       <c r="I189" s="6" t="inlineStr">
         <is>
@@ -8956,10 +8956,10 @@
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>1.018</v>
+        <v>0.523</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>1.113</v>
+        <v>0.533</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="7" t="inlineStr"/>
@@ -8972,28 +8972,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>-0.0694</v>
+        <v>6.74</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>832100</v>
+        <v>874700</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>0.49</v>
+        <v>0.2</v>
       </c>
       <c r="H190" t="n">
-        <v>45.33</v>
+        <v>48.5</v>
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
@@ -9001,10 +9001,10 @@
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>1.658</v>
+        <v>6.763</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>1.676</v>
+        <v>6.845</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="7" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         <v>-0.0383</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>821800</v>
+        <v>848200</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H191" t="n">
         <v>41.76</v>
@@ -9062,28 +9062,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>0.635</v>
+        <v>0.865</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0335</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>816000</v>
+        <v>842900</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>1.11</v>
+        <v>0.35</v>
       </c>
       <c r="H192" t="n">
-        <v>41.17</v>
+        <v>17.06</v>
       </c>
       <c r="I192" s="6" t="inlineStr">
         <is>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.644</v>
+        <v>1.018</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>0.626</v>
+        <v>1.113</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="7" t="inlineStr"/>
@@ -9107,28 +9107,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>0.78</v>
+        <v>1.61</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.0694</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>802000</v>
+        <v>833000</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="H193" t="n">
-        <v>46.17</v>
+        <v>45.33</v>
       </c>
       <c r="I193" s="6" t="inlineStr">
         <is>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.791</v>
+        <v>1.658</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>0.806</v>
+        <v>1.676</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="7" t="inlineStr"/>
@@ -9152,39 +9152,39 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>2.49</v>
+        <v>0.82</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>-0.004</v>
+        <v>-0.0353</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>789800</v>
+        <v>821100</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.24</v>
+        <v>0.57</v>
       </c>
       <c r="H194" t="n">
-        <v>33.04</v>
-      </c>
-      <c r="I194" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.84</v>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>2.572</v>
+        <v>0.838</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>2.722</v>
+        <v>0.773</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="7" t="inlineStr"/>
@@ -9197,28 +9197,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>0.82</v>
+        <v>0.635</v>
       </c>
       <c r="E195" s="3" t="n">
-        <v>-0.0353</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>788400</v>
+        <v>816000</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>0.54</v>
+        <v>1.11</v>
       </c>
       <c r="H195" t="n">
-        <v>48.84</v>
+        <v>41.17</v>
       </c>
       <c r="I195" s="6" t="inlineStr">
         <is>
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.838</v>
+        <v>0.644</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>0.773</v>
+        <v>0.626</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="7" t="inlineStr"/>
@@ -9242,39 +9242,39 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>1.04</v>
+        <v>0.78</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>-0.028</v>
+        <v>-0.0189</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>785000</v>
+        <v>802000</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>0.46</v>
+        <v>0.19</v>
       </c>
       <c r="H196" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="I196" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.17</v>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>1.058</v>
+        <v>0.791</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>1.19</v>
+        <v>0.806</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="7" t="inlineStr"/>
@@ -9287,39 +9287,39 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>APEX</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>-0.0167</v>
+        <v>2.5</v>
+      </c>
+      <c r="E197" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>777900</v>
+        <v>792600</v>
       </c>
       <c r="G197" s="5" t="n">
-        <v>9.82</v>
+        <v>0.24</v>
       </c>
       <c r="H197" t="n">
-        <v>42.33</v>
-      </c>
-      <c r="I197" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.99</v>
+      </c>
+      <c r="I197" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.618</v>
+        <v>2.573</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>0.637</v>
+        <v>2.723</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="7" t="inlineStr"/>
@@ -9332,39 +9332,39 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>0.925</v>
+        <v>1.04</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.028</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>776100</v>
+        <v>790200</v>
       </c>
       <c r="G198" s="5" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="H198" t="n">
-        <v>38.68</v>
-      </c>
-      <c r="I198" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.57</v>
+      </c>
+      <c r="I198" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J198" s="2" t="n">
-        <v>1.003</v>
+        <v>1.058</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>1.028</v>
+        <v>1.19</v>
       </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" s="7" t="inlineStr"/>
@@ -9377,28 +9377,28 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>0.535</v>
+        <v>0.925</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>-0.0183</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>766000</v>
+        <v>780400</v>
       </c>
       <c r="G199" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H199" t="n">
-        <v>31.42</v>
+        <v>38.68</v>
       </c>
       <c r="I199" s="6" t="inlineStr">
         <is>
@@ -9406,10 +9406,10 @@
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>0.579</v>
+        <v>1.003</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>0.62</v>
+        <v>1.028</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="7" t="inlineStr"/>
@@ -9422,28 +9422,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>APEX</t>
         </is>
       </c>
       <c r="D200" s="2" t="n">
-        <v>0.895</v>
+        <v>0.59</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>-0.0272</v>
+        <v>-0.0167</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>747500</v>
+        <v>777900</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>0.25</v>
+        <v>9.82</v>
       </c>
       <c r="H200" t="n">
-        <v>41.89</v>
+        <v>42.33</v>
       </c>
       <c r="I200" s="6" t="inlineStr">
         <is>
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.91</v>
+        <v>0.618</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>0.963</v>
+        <v>0.637</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" s="7" t="inlineStr"/>
@@ -9467,28 +9467,28 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>2.11</v>
+        <v>0.535</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>-0.0409</v>
+        <v>-0.0183</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>727300</v>
+        <v>766000</v>
       </c>
       <c r="G201" s="5" t="n">
-        <v>1.48</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H201" t="n">
-        <v>36.3</v>
+        <v>31.42</v>
       </c>
       <c r="I201" s="6" t="inlineStr">
         <is>
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="J201" s="2" t="n">
-        <v>2.265</v>
+        <v>0.579</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>2.221</v>
+        <v>0.62</v>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" s="7" t="inlineStr"/>
@@ -9512,39 +9512,39 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E202" s="9" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>726600</v>
+        <v>759900</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>1.03</v>
+        <v>0.23</v>
       </c>
       <c r="H202" t="n">
-        <v>57.41</v>
-      </c>
-      <c r="I202" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.74</v>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.999</v>
+        <v>0.964</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>0.981</v>
+        <v>1.019</v>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" s="7" t="inlineStr"/>
@@ -9557,28 +9557,28 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>0.905</v>
+        <v>0.895</v>
       </c>
       <c r="E203" s="3" t="n">
-        <v>-0.0163</v>
+        <v>-0.0272</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>721800</v>
+        <v>752700</v>
       </c>
       <c r="G203" s="5" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H203" t="n">
-        <v>41.27</v>
+        <v>41.89</v>
       </c>
       <c r="I203" s="6" t="inlineStr">
         <is>
@@ -9586,10 +9586,10 @@
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.921</v>
+        <v>0.91</v>
       </c>
       <c r="K203" s="2" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.963</v>
       </c>
       <c r="L203" t="inlineStr"/>
       <c r="M203" s="7" t="inlineStr"/>
@@ -9602,28 +9602,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D204" s="2" t="n">
-        <v>0.625</v>
+        <v>2.12</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0364</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>718500</v>
+        <v>727600</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>0.58</v>
+        <v>1.48</v>
       </c>
       <c r="H204" t="n">
-        <v>37.25</v>
+        <v>36.94</v>
       </c>
       <c r="I204" s="6" t="inlineStr">
         <is>
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.632</v>
+        <v>2.266</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>0.63</v>
+        <v>2.221</v>
       </c>
       <c r="L204" t="inlineStr"/>
       <c r="M204" s="7" t="inlineStr"/>
@@ -9647,39 +9647,39 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>-0.0303</v>
+        <v>1.01</v>
+      </c>
+      <c r="E205" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>697400</v>
+        <v>726600</v>
       </c>
       <c r="G205" s="5" t="n">
-        <v>0.39</v>
+        <v>1.03</v>
       </c>
       <c r="H205" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="I205" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.41</v>
+      </c>
+      <c r="I205" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>3.16</v>
+        <v>0.999</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>2.763</v>
+        <v>0.981</v>
       </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" s="7" t="inlineStr"/>
@@ -9692,28 +9692,28 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D206" s="2" t="n">
-        <v>1.58</v>
+        <v>0.905</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>-0.0247</v>
+        <v>-0.0163</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>688300</v>
+        <v>724800</v>
       </c>
       <c r="G206" s="5" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H206" t="n">
-        <v>33.84</v>
+        <v>41.27</v>
       </c>
       <c r="I206" s="6" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="J206" s="2" t="n">
-        <v>1.68</v>
+        <v>0.921</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>1.811</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" s="7" t="inlineStr"/>
@@ -9737,28 +9737,28 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ABMB</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D207" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E207" s="10" t="n">
-        <v>0.02</v>
+        <v>0.625</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>673800</v>
+        <v>718500</v>
       </c>
       <c r="G207" s="5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H207" t="n">
-        <v>37.35</v>
+        <v>37.25</v>
       </c>
       <c r="I207" s="6" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="J207" s="2" t="n">
-        <v>4.702</v>
+        <v>0.632</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>4.804</v>
+        <v>0.63</v>
       </c>
       <c r="L207" t="inlineStr"/>
       <c r="M207" s="7" t="inlineStr"/>
@@ -9782,28 +9782,28 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D208" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E208" s="10" t="n">
-        <v>0.0108</v>
+        <v>3.2</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>660200</v>
+        <v>697500</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="H208" t="n">
-        <v>36.74</v>
+        <v>57.28</v>
       </c>
       <c r="I208" s="6" t="inlineStr">
         <is>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>0.964</v>
+        <v>3.16</v>
       </c>
       <c r="K208" s="2" t="n">
-        <v>1.019</v>
+        <v>2.763</v>
       </c>
       <c r="L208" t="inlineStr"/>
       <c r="M208" s="7" t="inlineStr"/>
@@ -9827,28 +9827,28 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0308</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>KTI</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D209" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E209" s="10" t="n">
-        <v>0.0098</v>
+        <v>1.58</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>-0.0247</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>634200</v>
+        <v>689200</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>2.5</v>
+        <v>0.61</v>
       </c>
       <c r="H209" t="n">
-        <v>47.31</v>
+        <v>33.84</v>
       </c>
       <c r="I209" s="6" t="inlineStr">
         <is>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.517</v>
+        <v>1.68</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>0.528</v>
+        <v>1.811</v>
       </c>
       <c r="L209" t="inlineStr"/>
       <c r="M209" s="7" t="inlineStr"/>
@@ -9872,28 +9872,28 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>ABMB</t>
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>1.39</v>
+        <v>4.6</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>0.0146</v>
+        <v>0.02</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>632900</v>
+        <v>680500</v>
       </c>
       <c r="G210" s="5" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="H210" t="n">
-        <v>61.38</v>
+        <v>37.35</v>
       </c>
       <c r="I210" s="6" t="inlineStr">
         <is>
@@ -9901,10 +9901,10 @@
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>1.371</v>
+        <v>4.702</v>
       </c>
       <c r="K210" s="2" t="n">
-        <v>1.339</v>
+        <v>4.804</v>
       </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" s="7" t="inlineStr"/>
@@ -9917,39 +9917,39 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>0.545</v>
+        <v>1.06</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>-0.018</v>
+        <v>-0.0275</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>624800</v>
+        <v>679500</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="H211" t="n">
-        <v>30.92</v>
-      </c>
-      <c r="I211" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.58</v>
+      </c>
+      <c r="I211" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>0.582</v>
+        <v>1.144</v>
       </c>
       <c r="L211" t="inlineStr"/>
       <c r="M211" s="7" t="inlineStr"/>
@@ -9962,39 +9962,39 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>7.99</v>
+        <v>1.39</v>
       </c>
       <c r="E212" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0146</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>608000</v>
+        <v>640900</v>
       </c>
       <c r="G212" s="5" t="n">
-        <v>0.14</v>
+        <v>0.32</v>
       </c>
       <c r="H212" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I212" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.38</v>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J212" s="2" t="n">
-        <v>7.879</v>
+        <v>1.371</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>8.002000000000001</v>
+        <v>1.339</v>
       </c>
       <c r="L212" t="inlineStr"/>
       <c r="M212" s="7" t="inlineStr"/>
@@ -10007,28 +10007,28 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0308</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>KTI</t>
         </is>
       </c>
       <c r="D213" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E213" s="3" t="n">
-        <v>-0.0331</v>
+        <v>0.515</v>
+      </c>
+      <c r="E213" s="10" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>605700</v>
+        <v>634200</v>
       </c>
       <c r="G213" s="5" t="n">
-        <v>0.27</v>
+        <v>2.5</v>
       </c>
       <c r="H213" t="n">
-        <v>29.59</v>
+        <v>47.31</v>
       </c>
       <c r="I213" s="6" t="inlineStr">
         <is>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>1.278</v>
+        <v>0.517</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>1.309</v>
+        <v>0.528</v>
       </c>
       <c r="L213" t="inlineStr"/>
       <c r="M213" s="7" t="inlineStr"/>
@@ -10052,39 +10052,39 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D214" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>-0.0361</v>
+        <v>1.26</v>
+      </c>
+      <c r="E214" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>604100</v>
+        <v>632400</v>
       </c>
       <c r="G214" s="5" t="n">
-        <v>0.51</v>
+        <v>0.11</v>
       </c>
       <c r="H214" t="n">
-        <v>40.02</v>
-      </c>
-      <c r="I214" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.56</v>
+      </c>
+      <c r="I214" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>1.674</v>
+        <v>1.25</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>1.647</v>
+        <v>1.284</v>
       </c>
       <c r="L214" t="inlineStr"/>
       <c r="M214" s="7" t="inlineStr"/>
@@ -10097,28 +10097,28 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>0.875</v>
+        <v>0.545</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>-0.0489</v>
+        <v>-0.018</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>597300</v>
+        <v>625600</v>
       </c>
       <c r="G215" s="5" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="H215" t="n">
-        <v>33.21</v>
+        <v>30.92</v>
       </c>
       <c r="I215" s="6" t="inlineStr">
         <is>
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.957</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K215" s="2" t="n">
-        <v>1.01</v>
+        <v>0.582</v>
       </c>
       <c r="L215" t="inlineStr"/>
       <c r="M215" s="7" t="inlineStr"/>
@@ -10142,39 +10142,39 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>-0.0538</v>
+        <v>7.98</v>
+      </c>
+      <c r="E216" s="10" t="n">
+        <v>0.0101</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>595900</v>
+        <v>612800</v>
       </c>
       <c r="G216" s="5" t="n">
-        <v>0.82</v>
+        <v>0.14</v>
       </c>
       <c r="H216" t="n">
-        <v>58.66</v>
-      </c>
-      <c r="I216" s="8" t="inlineStr">
+        <v>54.61</v>
+      </c>
+      <c r="I216" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J216" s="2" t="n">
-        <v>1.732</v>
+        <v>7.878</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>1.61</v>
+        <v>8.002000000000001</v>
       </c>
       <c r="L216" t="inlineStr"/>
       <c r="M216" s="7" t="inlineStr"/>
@@ -10187,39 +10187,39 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>2.76</v>
+        <v>1.17</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>-0.0178</v>
+        <v>-0.0331</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>587300</v>
+        <v>605700</v>
       </c>
       <c r="G217" s="5" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H217" t="n">
-        <v>73.81999999999999</v>
-      </c>
-      <c r="I217" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.59</v>
+      </c>
+      <c r="I217" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J217" s="2" t="n">
-        <v>2.492</v>
+        <v>1.278</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>2.177</v>
+        <v>1.309</v>
       </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" s="7" t="inlineStr"/>
@@ -10232,28 +10232,28 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>YTLREIT</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D218" s="2" t="n">
-        <v>0.96</v>
+        <v>1.6</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>-0.0154</v>
+        <v>-0.0361</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>582900</v>
+        <v>604300</v>
       </c>
       <c r="G218" s="5" t="n">
-        <v>0.83</v>
+        <v>0.51</v>
       </c>
       <c r="H218" t="n">
-        <v>33.07</v>
+        <v>40.02</v>
       </c>
       <c r="I218" s="6" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.983</v>
+        <v>1.674</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>1</v>
+        <v>1.647</v>
       </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" s="7" t="inlineStr"/>
@@ -10277,39 +10277,39 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D219" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E219" s="9" t="n">
-        <v>0</v>
+        <v>0.875</v>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>-0.0489</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>560400</v>
+        <v>597800</v>
       </c>
       <c r="G219" s="5" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="H219" t="n">
-        <v>50.56</v>
-      </c>
-      <c r="I219" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.21</v>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>1.25</v>
+        <v>0.957</v>
       </c>
       <c r="K219" s="2" t="n">
-        <v>1.284</v>
+        <v>1.01</v>
       </c>
       <c r="L219" t="inlineStr"/>
       <c r="M219" s="7" t="inlineStr"/>
@@ -10322,39 +10322,39 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D220" s="2" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.0538</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>551500</v>
+        <v>596900</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="H220" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="I220" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.66</v>
+      </c>
+      <c r="I220" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J220" s="2" t="n">
-        <v>1.775</v>
+        <v>1.732</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>1.913</v>
+        <v>1.61</v>
       </c>
       <c r="L220" t="inlineStr"/>
       <c r="M220" s="7" t="inlineStr"/>
@@ -10367,39 +10367,39 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D221" s="2" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E221" s="10" t="n">
-        <v>0.0221</v>
+        <v>2.76</v>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>532300</v>
+        <v>590300</v>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1.08</v>
+        <v>0.36</v>
       </c>
       <c r="H221" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="I221" s="8" t="inlineStr">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="I221" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0.667</v>
+        <v>2.492</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>0.652</v>
+        <v>2.177</v>
       </c>
       <c r="L221" t="inlineStr"/>
       <c r="M221" s="7" t="inlineStr"/>
@@ -10412,39 +10412,39 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>YTLREIT</t>
         </is>
       </c>
       <c r="D222" s="2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E222" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.96</v>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>516400</v>
+        <v>582900</v>
       </c>
       <c r="G222" s="5" t="n">
-        <v>0.17</v>
+        <v>0.83</v>
       </c>
       <c r="H222" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I222" s="8" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.07</v>
+      </c>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J222" s="2" t="n">
-        <v>7.892</v>
+        <v>0.983</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>7.855</v>
+        <v>1</v>
       </c>
       <c r="L222" t="inlineStr"/>
       <c r="M222" s="7" t="inlineStr"/>
@@ -10457,28 +10457,28 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0351</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>LSH</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D223" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E223" s="3" t="n">
-        <v>-0.0809</v>
+        <v>1.67</v>
+      </c>
+      <c r="E223" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>501000</v>
+        <v>556700</v>
       </c>
       <c r="G223" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="H223" t="n">
-        <v>44.16</v>
+        <v>30.92</v>
       </c>
       <c r="I223" s="6" t="inlineStr">
         <is>
@@ -10486,16 +10486,151 @@
         </is>
       </c>
       <c r="J223" s="2" t="n">
-        <v>1.648</v>
+        <v>1.776</v>
       </c>
       <c r="K223" s="2" t="n">
-        <v>1.613</v>
+        <v>1.914</v>
       </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" s="7" t="inlineStr"/>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E224" s="10" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F224" s="4" t="n">
+        <v>537300</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H224" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="I224" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K224" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" s="7" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E225" s="10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F225" s="4" t="n">
+        <v>523700</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H225" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="I225" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="n">
+        <v>7.892</v>
+      </c>
+      <c r="K225" s="2" t="n">
+        <v>7.855</v>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" s="7" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>0351</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>LSH</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>-0.0751</v>
+      </c>
+      <c r="F226" s="4" t="n">
+        <v>521000</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H226" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="n">
+        <v>1.649</v>
+      </c>
+      <c r="K226" s="2" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M223"/>
+  <autoFilter ref="A1:M226"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>